--- a/Bang-mo-ta-De-an-VTVL-THPT-Phuc-Hoa-ND232-2026.xlsx
+++ b/Bang-mo-ta-De-an-VTVL-THPT-Phuc-Hoa-ND232-2026.xlsx
@@ -7,11 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Đề án &amp; Căn cứ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tổng hợp Phụ lục I (35 BC)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Mau Ban Mo Ta - Chuyen Mon" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Mau Ban Mo Ta - Ho Tro" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Khung Nang Luc &amp; KPI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Đề án &amp; Căn cứ NĐ 232" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Phụ lục I - DM 35 VTVL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. DM1 - VTVL Quản lý" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. DM2 - VTVL 13 Môn học" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. DM3 - VTVL 06 Hỗ trợ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Mau Mo Ta Chuan ND 232" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Khung năng lực 3 Nhóm" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. KPI đo lường 3 Nhóm" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -72,16 +75,16 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <sz val="10"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +107,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FEF3C7"/>
         <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
+        <bgColor rgb="002563EB"/>
       </patternFill>
     </fill>
     <fill>
@@ -171,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -209,22 +218,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,7 +230,16 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -647,7 +653,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>(Xây dựng theo Nghị định 232/2026/NĐ-CP &amp; Mẫu bản mô tả VTVL chuẩn - Tổng 35 biên chế)</t>
+          <t>(Xây dựng theo Nghị định 232/2026/NĐ-CP &amp; Phụ lục I C3 Phục Hòa - Tổng 35 biên chế)</t>
         </is>
       </c>
     </row>
@@ -857,9 +863,9 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>- Nhóm I (Viên chức quản lý): 07 người
-- Nhóm II (Viên chức chuyên môn, nghiệp vụ): 22 người (13 môn học)
-- Nhóm III (Viên chức hỗ trợ): 06 người</t>
+          <t>- Nhóm I (Viên chức quản lý): 07 người (Hiệu trưởng 1, Phó HT 2, TTCM 2, TPCM 2)
+- Nhóm II (Viên chức chuyên môn, nghiệp vụ): 22 người (13 môn học trong phụ lục)
+- Nhóm III (Viên chức hỗ trợ): 06 người (Kế toán 1, Văn thư 1, TB-TN 1, Giáo vụ 1, Y tế 1, Thủ quỹ 1)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
@@ -879,7 +885,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Toàn bộ bản mô tả VTVL được lập đúng theo Mẫu tại Phần B Phụ lục IV/VI của Nghị định số 232/2026/NĐ-CP.</t>
+          <t>Toàn bộ bản mô tả VTVL được lập chuẩn theo 6 cột nghiệp vụ và Phần B Phụ lục IV/VI của Nghị định số 232/2026/NĐ-CP.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
@@ -911,7 +917,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -922,7 +928,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>DANH MỤC VỊ TRÍ VIỆC LÀM VÀ BẬC NGHỀ NGHIỆP SỬ DỤNG TRƯỜNG THPT PHỤC HÒA</t>
+          <t>DANH MỤC VỊ TRÍ VIỆC LÀM VÀ BẬC NGHỀ NGHIỆP TRƯỜNG THPT PHỤC HÒA</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1158,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Vị trí việc làm viên chức chuyên môn, nghiệp vụ: 22 người</t>
+          <t>Vị trí việc làm viên chức chuyên môn, nghiệp vụ: 22 người (13 môn)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr"/>
@@ -1202,7 +1208,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Dạy Ngữ văn 10, 11, 12, ôn thi TN THPT</t>
+          <t>Dạy Ngữ văn 10, 11, 12, bồi dưỡng HSG Văn</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1282,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Dạy Ngoại ngữ, phát triển năng lực giao tiếp</t>
+          <t>Dạy Ngoại ngữ, phòng lab, giao tiếp</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1356,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Dạy Giáo dục thể chất, HKPĐ, rèn thể lực</t>
+          <t>Dạy GD Thể chất, Hội khỏe Phù Đổng</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1393,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Dạy GDQP-AN, hội thao QP-AN, an ninh quốc gia</t>
+          <t>Dạy GDQP-AN, hội thao, chủ quyền biên giới</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1430,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Dạy Địa lí, bảo vệ tài nguyên môi trường</t>
+          <t>Dạy Địa lí, Atlat, GIS, tài nguyên môi trường</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1467,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Dạy Giáo dục kinh tế và pháp luật</t>
+          <t>Dạy GD Kinh tế &amp; Pháp luật, xử lý tình huống</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1541,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Dạy Hóa học, thực hành hóa nghiệm, PCCC</t>
+          <t>Dạy Hóa học, thực hành phòng TN, PCCC</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1578,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Dạy Sinh học, thực hành phòng thí nghiệm Sinh</t>
+          <t>Dạy Sinh học, kính hiển vi, vườn thực nghiệm</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1652,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Dạy Tin học, phòng máy tính, CĐS &amp; AI</t>
+          <t>Dạy Tin học, lập trình Python, phòng máy, AI</t>
         </is>
       </c>
     </row>
@@ -1949,540 +1955,356 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
-    <col width="68" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="49" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>SỞ GIÁO DỤC VÀ ĐÀO TẠO CAO BẰNG
-TRƯỜNG THPT PHỤC HÒA</t>
-        </is>
-      </c>
-      <c r="C1" s="13" t="inlineStr">
-        <is>
-          <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM
-Độc lập – Tự do – Hạnh phúc
-_______________________</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>DANH MỤC 1: BẢN MÔ TẢ VỊ TRÍ VIỆC LÀM VIÊN CHỨC QUẢN LÝ (07 NGƯỜI)</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>BẢN MÔ TẢ CÔNG VIỆC VÀ KHUNG NĂNG LỰC VỊ TRÍ VIỆC LÀM</t>
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Vị trí việc làm &amp; Mã số</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Nhiệm vụ quản lý chính</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Nội dung công việc cụ thể &amp; Tiêu chí đo lường</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Tỷ trọng</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Sản phẩm / Kết quả đầu ra</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>(Mẫu chuẩn theo Phần B Phụ lục IV/VI Nghị định số 232/2026/NĐ-CP - Áp dụng cho VTVL Giáo viên THPT 13 Môn học)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Hiệu trưởng
+(HT-THPT-01)
+Phụ cấp: 0.70 | 01 người
+Định mức: 02 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>1. Chiến lược &amp; Kế hoạch phát triển</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>- Xây dựng Chiến lược 5 năm, Kế hoạch năm học trình cấp có thẩm quyền phê duyệt.
+- Ban hành Quy chế dân chủ, Quy chế chi tiêu nội bộ, Quy chế làm việc của trường.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>- Chiến lược phát triển trường 5 năm.
+- Kế hoạch năm học &amp; Quy chế làm việc.
+- Báo cáo định kỳ Sở GD&amp;ĐT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Hiệu trưởng
+(HT-THPT-01)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>2. Quản lý nhân sự &amp; Đánh giá thi đua</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>- Phân công nhiệm vụ, bổ nhiệm tổ trưởng, tổ phó; đánh giá xếp loại VC hàng năm theo NĐ 232/2026/NĐ-CP.
+- Thực hiện công tác quy hoạch, đào tạo, bồi dưỡng và thi đua khen thưởng.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>- QĐ phân công nhiệm vụ cán bộ giáo viên.
+- QĐ xếp loại thi đua, khen thưởng viên chức.
+- Hồ sơ quy hoạch cán bộ quản lý.</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>I. THÔNG TIN CHUNG</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Hiệu trưởng
+(HT-THPT-01)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>3. Quản lý tài chính &amp; Cơ sở vật chất</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>- Chủ tài khoản, duyệt thu - chi ngân sách, kiểm tra công tác kế toán, quản lý tài sản công đúng luật.
+- Chỉ đạo sửa chữa, nâng cấp CSVC trường học bảo đảm dạy và học an toàn.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>- Dự toán &amp; Báo cáo quyết toán ngân sách.
+- Quy chế chi tiêu nội bộ chuẩn hóa.
+- Báo cáo kiểm kê tài sản hàng năm.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Tên vị trí việc làm:</t>
+          <t>Hiệu trưởng
+(HT-THPT-01)</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Giáo viên trung học phổ thông (Môn học: 13 Môn trong Phụ lục I)</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
+          <t>4. Chỉ đạo chuyên môn &amp; Giảng dạy</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>- Chỉ đạo kỳ thi tốt nghiệp THPT, kỳ thi chọn HSG; trực tiếp giảng dạy 02 tiết/tuần theo quy định.
+- Thanh tra nội bộ, dự giờ thăm lớp, đổi mới PPDH và ứng dụng AI toàn trường.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>- Báo cáo kết quả kỳ thi tốt nghiệp THPT.
+- Sổ giáo án cá nhân giảng dạy 02 tiết/tuần.
+- Biên bản kiểm tra chuyên môn nội bộ.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Nhóm vị trí việc làm:</t>
+          <t>Phó Hiệu trưởng
+(PHT-THPT-01)
+Phụ cấp: 0.50 | 02 người
+Định mức: 04 tiết/tuần</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Chuyên môn, nghiệp vụ (Mã số: GV-THPT-01)</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
+          <t>1. Chỉ đạo &amp; điều hành chuyên môn</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>- Thẩm định và duyệt Kế hoạch giáo dục nhà trường, kế hoạch các tổ CM theo CT GDPT 2018.
+- Chỉ đạo đổi mới phương pháp dạy học, giáo dục STEM/STEAM, chuyển đổi số dạy học.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chuyên môn năm học được phê duyệt.
+- Lịch thi, thời khóa biểu toàn trường.
+- Báo cáo sơ kết, tổng kết chuyên môn.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Bậc nghề nghiệp sử dụng:</t>
+          <t>Phó Hiệu trưởng
+(PHT-THPT-01)</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Bậc 3 đến Bậc 4 (theo Phụ lục I Trường THPT Phục Hòa)</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
+          <t>2. Khảo thí, ôn thi TN &amp; Ký số học bạ</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>- Xây dựng ma trận đặc tả, ngân hàng đề kiểm tra định kỳ; quản lý ôn thi TN THPT khối 12.
+- Kiểm tra, ký duyệt học bạ điện tử, kiểm tra hồ sơ giáo án giáo viên; dạy 04 tiết/tuần.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>- Ngân hàng đề kiểm tra định kỳ chuẩn quy chế.
+- Kế hoạch ôn thi TN THPT chi tiết theo môn.
+- 100% học bạ số được duyệt đúng hạn.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Lĩnh vực hoạt động:</t>
+          <t>Tổ trưởng CM
+(TTCM-THPT-01)
+Phụ cấp: 0.25 | 02 người
+Định mức: 14 tiết/tuần</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Giáo dục trung học phổ thông - Giảng dạy và giáo dục học sinh</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
+          <t>1. Quản lý toàn diện chuyên môn tổ</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>- Xây dựng kế hoạch dạy học môn học (PL1, PL2, PL3) theo CT GDPT 2018; phân công GV dạy đúng chuyên ngành.
+- Tổ chức sinh hoạt chuyên môn theo NCBL (≥ 2 lần/tháng); kiểm tra giáo án, dự giờ GV.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch giáo dục tổ chuyên môn.
+- Biên bản họp sinh hoạt chuyên môn theo NCBL.
+- Phiếu đánh giá giáo viên trong tổ.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Đơn vị:</t>
+          <t>Tổ phó CM
+(TPCM-THPT-01)
+Phụ cấp: 0.15 | 02 người
+Định mức: 16 tiết/tuần</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Trường THPT Phục Hòa, huyện Phục Hòa, tỉnh Cao Bằng</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Cấp quản lý:</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Hiệu trưởng, Phó Hiệu trưởng phụ trách chuyên môn, Tổ trưởng chuyên môn</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Vị trí việc làm liên quan:</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Tổ trưởng CM, Tổ phó CM, Giáo viên chủ nhiệm, Thư viện, Thiết bị TN, Giáo vụ</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Số lượng người đảm nhiệm:</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>22 người (gồm: Ngữ văn: 3, Toán: 3, Anh: 2, Sử: 2, GDTC: 2, GDQP: 1, Địa: 2, KTPL: 1, Lý: 1, Hóa: 1, Sinh: 1, CN: 2, Tin: 1)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>II. MỤC TIÊU VỊ TRÍ VIỆC LÀM</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Công thức mục tiêu:</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Trực tiếp giảng dạy, giáo dục học sinh theo Chương trình GDPT 2018 nhằm phát triển toàn diện phẩm chất, năng lực của học sinh THPT; bảo đảm hoàn thành chỉ tiêu chất lượng bộ môn và mục tiêu giáo dục của trường THPT Phục Hòa.</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>III. CÔNG VIỆC, KẾT QUẢ, SẢN PHẨM CHUYÊN MÔN (Bảng theo Bậc nghề nghiệp)</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Bậc</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Nội dung công việc chuyên môn</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Sản phẩm, Kết quả đầu ra</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>Tiêu chí đánh giá</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>Môn học áp dụng</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Bậc 3</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>1. Giảng dạy môn học theo CT GDPT 2018 (định mức 17 tiết/tuần).
-2. Xây dựng Kế hoạch bài dạy (giáo án), đổi mới PPDH tích cực, tích hợp STEM.
-3. Kiểm tra đánh giá học sinh thường xuyên và định kỳ, vào điểm số điện tử đúng hạn.
-4. Thực hiện công tác giáo viên chủ nhiệm, quản lý nề nếp lớp được phân công.
-5. Bồi dưỡng học sinh yếu, phụ đạo học sinh có nguy cơ chưa đạt chuẩn.</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>- 100% tiết dạy có giáo án chuẩn bị kỹ lưỡng trước khi lên lớp.
-- Sổ theo dõi đánh giá học sinh cập nhật chính xác.
-- Học sinh đạt chuẩn môn học ≥ 95%.
-- Học bạ điện tử được nhận xét và ký số đúng thời hạn.</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Chất lượng giảng dạy; tính độc lập sư phạm; khả năng giải quyết các tình huống sư phạm thông thường; tuân thủ đúng tiến độ chương trình GDPT 2018.</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Toàn bộ 13 môn học</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Bậc 4</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>1. Thực hiện giảng dạy các chuyên đề nâng cao, dạy ôn thi tốt nghiệp THPT khối 12.
-2. Chủ trì hoặc nòng cốt tổ chức sinh hoạt chuyên môn theo NCBL cấp tổ/trường.
-3. Xây dựng đề kiểm tra định kỳ, ma trận đề, ngân hàng câu hỏi chuẩn quy chế.
-4. Trực tiếp bồi dưỡng đội tuyển học sinh giỏi môn học dự thi cấp tỉnh.
-5. Đổi mới sáng tạo: Có sáng kiến kinh nghiệm, bài học STEM hoặc ứng dụng AI xuất sắc được công nhận.</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>- Ngân hàng câu hỏi ma trận đề thi chuẩn mực.
-- Có học sinh đạt giải HSG môn học cấp tỉnh.
-- Tỷ lệ tốt nghiệp THPT môn học đạt ≥ 98%.
-- Báo cáo chuyên đề đổi mới PPDH hoặc sáng kiến cấp cơ sở được nghiệm thu.</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Hiệu quả tổ chức chuyên môn; năng lực hướng dẫn đồng nghiệp; khả năng chuẩn hóa học liệu số; kết quả thi HSG và tốt nghiệp THPT vượt chỉ tiêu giao.</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Giáo viên cốt cán 13 môn</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>IV. CÔNG VIỆC, KẾT QUẢ, SẢN PHẨM QUẢN LÝ</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Không áp dụng đối với vị trí Giáo viên chuyên môn</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>V. CÔNG VIỆC, KẾT QUẢ, SẢN PHẨM HỖ TRỢ</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Không áp dụng đối với vị trí Giáo viên chuyên môn</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>VI. KHUNG NĂNG LỰC VỊ TRÍ VIỆC LÀM</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>1. Năng lực chung:
- - Phẩm chất đạo đức nhà giáo, chấp hành pháp luật, tinh thần phụng sự học sinh (Cấp độ 4 - 5)
- - Giao tiếp ứng xử sư phạm thân thiện với phụ huynh và học sinh (Cấp độ 4)
- - Đổi mới sáng tạo và áp dụng công nghệ số, AI vào soạn giảng (Cấp độ 4)
- - Kỹ năng sử dụng công nghệ thông tin, ngoại ngữ chuyên ngành (Cấp độ 3 - 4)
-2. Năng lực chuyên môn:
- - Nắm vững kiến thức 13 môn học GDPT 2018 (Cấp độ 4 - 5)
- - Phương pháp dạy học tích cực, giáo dục STEM (Cấp độ 4 - 5)
- - Kiểm tra đánh giá năng lực học sinh (Cấp độ 4)</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>VII. MỐI QUAN HỆ CÔNG TÁC</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>1. Bên trong: Báo cáo trực tiếp Tổ trưởng CM, Phó Hiệu trưởng, Hiệu trưởng; phối hợp với GV chủ nhiệm, GV bộ môn khác, nhân viên Thiết bị, Thư viện, Y tế, Giáo vụ.
-2. Bên ngoài: Phối hợp thường xuyên với Cha mẹ học sinh (CMHS); Hội Khuyến học địa phương; Sở GD&amp;ĐT (khi tham gia hội đồng thi, tập huấn chuyên môn).</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>VIII. PHẠM VI QUYỀN HẠN</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>1. Về chuyên môn: Được chủ động lựa chọn phương pháp dạy học, kiểm tra đánh giá theo kế hoạch giáo dục môn học; đánh giá xếp loại học sinh theo quy chế; tham gia biên soạn tài liệu giáo dục địa phương.
-2. Về quản lý: Quản lý học sinh trong giờ học và các hoạt động giáo dục phân công.
-3. Về tài chính: Được bảo đảm trang thiết bị dạy học, phòng bộ môn, chế độ thừa giờ, bồi dưỡng theo quy định.</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>IX. YÊU CẦU VỀ TRÌNH ĐỘ, KINH NGHIỆM, PHẨM CHẤT</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>- Trình độ đào tạo: Bằng Cử nhân (Đại học) sư phạm trở lên đúng chuyên ngành môn học giảng dạy (Ngữ văn, Toán, Tiếng Anh, Lịch sử, Thể dục, Địa lý, Vật lý, Hóa học, Sinh học, Kỹ thuật công nghiệp/nông nghiệp, Tin học).
-- Bồi dưỡng: Có chứng chỉ bồi dưỡng theo tiêu chuẩn chức danh nghề nghiệp giáo viên THPT.
-- Ngoại ngữ &amp; Tin học: Năng lực ngoại ngữ và tin học đạt chuẩn theo quy định hiện hành; làm chủ ký số học bạ.
-- Phẩm chất: Yêu nghề, tận tụy, mẫu mực, tâm huyết với sự nghiệp giáo dục vùng cao Phục Hòa.</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>NGƯỜI LẬP BIỂU
-(Ký và ghi rõ họ tên)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>Phục Hòa, ngày .... tháng .... năm 2026
-HIỆU TRƯỞNG
-(Ký tên, đóng dấu)</t>
+          <t>1. Quản lý nề nếp, sổ sách &amp; tiến độ</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>- Theo dõi tiến độ chương trình hàng tuần, lịch báo giảng điện tử, kế hoạch dạy thay/bù của tổ viên.
+- Kiểm tra nề nếp hồ sơ sổ sách, đôn đốc ký số học bạ; giảng dạy 16 tiết/tuần.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>- Sổ theo dõi tiến độ chương trình hàng tuần.
+- Biên bản kiểm tra nề nếp hồ sơ chuyên môn.
+- Báo cáo tổng hợp nề nếp tổ viên.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C10:E10"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2494,572 +2316,1807 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
-    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
     <col width="68" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="68" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>SỞ GIÁO DỤC VÀ ĐÀO TẠO CAO BẰNG
-TRƯỜNG THPT PHỤC HÒA</t>
-        </is>
-      </c>
-      <c r="C1" s="13" t="inlineStr">
-        <is>
-          <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM
-Độc lập – Tự do – Hạnh phúc
-_______________________</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>DANH MỤC 2: BẢNG MÔ TẢ VỊ TRÍ VIỆC LÀM VIÊN CHỨC CHUYÊN MÔN THEO 13 MÔN HỌC (22 BIÊN CHẾ)</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>BẢN MÔ TẢ CÔNG VIỆC VÀ KHUNG NĂNG LỰC VỊ TRÍ VIỆC LÀM HỖ TRỢ</t>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Vị trí việc làm &amp; Mã số</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Nhiệm vụ quản lý chính</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Nội dung công việc cụ thể &amp; Tiêu chí đo lường</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Tỷ trọng</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Sản phẩm / Kết quả đầu ra</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>(Mẫu chuẩn theo Phần B Phụ lục IV/VI Nghị định số 232/2026/NĐ-CP - Áp dụng cho 06 Viên chức hỗ trợ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+      <c r="A4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Ngữ văn
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 03 biên chế
+Định mức: 17 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>1. Giảng dạy môn Ngữ văn &amp; Đổi mới KTĐG</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy môn Ngữ văn 10, 11, 12 theo CT GDPT 2018 (định mức 17 tiết/tuần).
+- Rèn luyện 4 kỹ năng Đọc - Viết - Nói - Nghe; đổi mới PPDH tác phẩm văn học, tích hợp ngữ liệu địa phương Cao Bằng.
+- Đổi mới ra đề kiểm tra đánh giá theo hướng phát triển năng lực, tránh sao chép văn mẫu.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy (giáo án) môn Văn chuẩn bị chu đáo.
+- Đề kiểm tra định kỳ có ma trận đặc tả.
+- Học bạ và sổ điểm điện tử cập nhật đúng hạn.
+- Tỷ lệ học sinh đạt chuẩn môn Văn ≥ 98%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Ngữ văn (tiếp)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>2. Công tác chủ nhiệm &amp; Giáo dục đạo đức</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>- Quản lý toàn diện học sinh lớp chủ nhiệm, xây dựng tập thể lớp đoàn kết, kỷ cương.
+- Phối hợp chặt chẽ với cha mẹ học sinh qua sổ liên lạc điện tử; ký duyệt học bạ số.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Biên bản họp CMHS đầu năm, cuối kỳ.
+- Sổ theo dõi nề nếp học sinh.
+- Học bạ số ký duyệt đầy đủ.</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>I. THÔNG TIN CHUNG</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n"/>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="18" t="n"/>
+      <c r="A6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Ngữ văn (tiếp)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>3. Bồi dưỡng chuyên môn, NCBL &amp; Trợ lý AI</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>- Tham gia sinh hoạt chuyên môn theo NCBL đầy đủ (≥ 2 lần/tháng); dự giờ đồng nghiệp.
+- Ứng dụng công nghệ thông tin và AI (trợ lý AI gợi ý ngữ liệu văn học, tóm tắt tác phẩm, đề đọc hiểu).</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>- Sổ tích lũy chuyên môn cá nhân.
+- Phiếu dự giờ đồng nghiệp (≥ 1 tiết/kỳ).
+- Kho học liệu số môn Văn đóng góp cho tổ.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Tên nhóm vị trí:</t>
+      <c r="A7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Ngữ văn (tiếp)</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Viên chức hỗ trợ (Gồm: Kế toán, Văn thư, Thiết bị TN, Giáo vụ, Y tế học đường, Thủ quỹ)</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
+          <t>4. Bồi dưỡng HSG môn Văn &amp; Ôn thi tốt nghiệp</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>- Bồi dưỡng đội tuyển HSG môn Ngữ văn dự thi cấp tỉnh theo kế hoạch.
+- Phụ đạo học sinh yếu kém, phụ đạo ôn thi tốt nghiệp THPT khối 12 đạt phổ điểm cao.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>- Giáo án bồi dưỡng HSG và phụ đạo.
+- Học sinh đạt giải HSG môn Văn cấp tỉnh.
+- Tỷ lệ tốt nghiệp THPT môn Văn đạt ≥ 98.5%.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A8" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Nhóm vị trí việc làm:</t>
+          <t>Giáo viên môn Toán
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 03 biên chế
+Định mức: 17 tiết/tuần</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Hỗ trợ, phục vụ (Định mức làm việc: 40 giờ/tuần)</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
+          <t>1. Giảng dạy môn Toán &amp; Mô hình hóa thực tiễn</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy môn Toán 10, 11, 12 (Đại số, Giải tích, Hình học, Xác suất - Thống kê) theo định mức 17 tiết/tuần.
+- Phát triển tư duy logic, mô hình hóa toán học; ứng dụng phần mềm GeoGebra vẽ hình động, máy tính bỏ túi; dạy học STEM tích hợp Toán học.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy môn Toán chất lượng cao.
+- Ngân hàng câu hỏi trắc nghiệm đúng/sai, trả lời ngắn theo cấu trúc mới.
+- Tỷ lệ HS đạt chuẩn môn Toán ≥ 96%.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Bậc nghề nghiệp sử dụng:</t>
+      <c r="A9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Toán (tiếp)</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Bậc 1 đến Bậc 4 (theo Phụ lục I Trường THPT Phục Hòa)</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
+          <t>2. Công tác chủ nhiệm &amp; Tư vấn hướng nghiệp KHTN</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>- Chủ nhiệm lớp, nắm bắt tâm lý học sinh, duy trì nề nếp kỷ luật lớp.
+- Tư vấn hướng nghiệp và định hướng lựa chọn tổ hợp môn KHTN / thi đại học.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Sổ theo dõi học sinh lớp chủ nhiệm.
+- Học bạ số được nhận xét và ký duyệt đúng hạn.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Lĩnh vực hoạt động:</t>
+      <c r="A10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Toán (tiếp)</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Tài chính, hành chính, thư viện số, thiết bị dạy học, giáo vụ, y tế học đường, ngân quỹ</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
+          <t>3. Sinh hoạt NCBL &amp; Ứng dụng AI tạo đề thi</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>- Sinh hoạt chuyên môn theo NCBL; tự làm thiết bị dạy học số.
+- Ứng dụng AI sinh đề trắc nghiệm theo 4 mức độ nhận thức của Bộ GD&amp;ĐT.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>- Phiếu dự giờ đồng nghiệp.
+- Bộ bài giảng điện tử tương tác môn Toán.
+- Bài học STEM môn Toán được nghiệm thu.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Đơn vị:</t>
+      <c r="A11" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Toán (tiếp)</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Trường THPT Phục Hòa, huyện Phục Hòa, tỉnh Cao Bằng</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
+          <t>4. Bồi dưỡng HSG Toán &amp; Ôn thi TN THPT</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>- Bồi dưỡng đội tuyển HSG Toán dự thi cấp tỉnh; phụ đạo học sinh có nguy cơ hổng kiến thức.
+- Trực tiếp giảng dạy ôn thi tốt nghiệp THPT môn Toán đạt phổ điểm khá giỏi.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>- Chuyên đề bồi dưỡng HSG Toán.
+- Học sinh đạt giải HSG Toán cấp tỉnh.
+- Phổ điểm tốt nghiệp môn Toán đạt bình quân ≥ 6.8.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A12" s="7" t="n">
+        <v>9</v>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Cấp quản lý:</t>
+          <t>Giáo viên môn Ngoại ngữ (Tiếng Anh)
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 02 biên chế
+Định mức: 17 tiết/tuần</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Hiệu trưởng, Phó Hiệu trưởng trực tiếp phụ trách cơ sở vật chất và văn phòng</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
+          <t>1. Giảng dạy môn Ngoại ngữ &amp; Phòng Lab tiếng</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy Tiếng Anh 10, 11, 12 theo khung năng lực 6 bậc Việt Nam (định mức 17 tiết/tuần).
+- Rèn luyện kỹ năng Nghe - Nói - Đọc - Viết; sử dụng phòng lab học tiếng, học liệu âm thanh đa phương tiện; tạo môi trường giao tiếp tiếng Anh tự nhiên.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy Tiếng Anh tương tác.
+- File âm thanh bài kiểm tra kỹ năng nghe/nói.
+- Đề kiểm tra trắc nghiệm theo chuẩn cấu trúc mới.
+- Tỷ lệ HS đạt chuẩn môn Ngoại ngữ ≥ 95%.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Số lượng người đảm nhiệm:</t>
+      <c r="A13" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Ngoại ngữ (Tiếng Anh) (tiếp)</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>06 người (Kế toán: 1, Văn thư: 1, Thiết bị TN: 1, Giáo vụ: 1, Y tế: 1, Thủ quỹ: 1)</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
+          <t>2. Chủ nhiệm lớp &amp; Thúc đẩy CLB Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>- Công tác chủ nhiệm, quản lý nề nếp lớp; thúc đẩy học sinh tham gia Câu lạc bộ Tiếng Anh và hoạt động ngoại khóa giao lưu quốc tế.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Kế hoạch và sản phẩm sinh hoạt CLB Tiếng Anh.
+- Học bạ số ký duyệt đúng hạn.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>II. MỤC TIÊU VỊ TRÍ VIỆC LÀM</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
+      <c r="A14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Ngoại ngữ (Tiếng Anh) (tiếp)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>3. Tự bồi dưỡng chuẩn C1 &amp; Ứng dụng AI luyện nói</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>- Nâng cao năng lực sư phạm tiếng Anh theo chuẩn Châu Âu (C1/B2); tham gia sinh hoạt chuyên môn cụm.
+- Ứng dụng AI luyện phát âm tiếng Anh và tạo bài tập giao tiếp.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>- Chứng chỉ bồi dưỡng chuyên môn.
+- Kho học liệu nghe nhìn tiếng Anh số hóa.
+- Phiếu dự giờ đồng nghiệp.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Công thức mục tiêu:</t>
+      <c r="A15" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Ngoại ngữ (Tiếng Anh) (tiếp)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Thực hiện các hoạt động hỗ trợ về tài chính, văn thư lưu trữ, quản lý thiết bị dạy học, hồ sơ học sinh, chăm sóc y tế ban đầu và quản lý quỹ tiền mặt nhằm bảo đảm các điều kiện vận hành thông suốt, an toàn và đúng pháp luật của trường THPT Phục Hòa.</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
+          <t>4. Bồi dưỡng HSG Tiếng Anh &amp; Ôn thi tốt nghiệp</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>- Bồi dưỡng HSG Tiếng Anh thi cấp tỉnh; phụ đạo học sinh có nguy cơ trượt tốt nghiệp.
+- Hướng dẫn học sinh tiếp cận chứng chỉ quốc tế (IELTS/VSTEP).</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>- Đội tuyển HSG Tiếng Anh có giải cấp tỉnh.
+- Học sinh vùng cao tự tin vượt qua kỳ thi TN THPT môn Tiếng Anh.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>V. CÔNG VIỆC, KẾT QUẢ, SẢN PHẨM HỖ TRỢ (Bảng theo Bậc nghề nghiệp cho 06 Vị trí)</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
+      <c r="A16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Lịch sử
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 02 biên chế
+Định mức: 17 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>1. Giảng dạy môn Lịch sử &amp; Giáo dục truyền thống</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy Lịch sử bắt buộc và các chuyên đề lựa chọn (17 tiết/tuần).
+- Giáo dục lòng yêu nước, tự hào dân tộc, gắn liền di tích lịch sử chiến thắng Biên giới và truyền thống cách mạng quê hương Cao Bằng.
+- Đổi mới PPDH, phát triển năng lực tìm hiểu và nhận thức lịch sử.</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy Lịch sử đổi mới phương pháp.
+- Sơ đồ tư duy dòng thời gian lịch sử số hóa.
+- Đề kiểm tra định kỳ có ma trận chuẩn.
+- Tỷ lệ HS đạt chuẩn môn Sử ≥ 98%.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>Vị trí &amp; Bậc</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>Nội dung công việc hỗ trợ cốt lõi</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>Sản phẩm, Kết quả đầu ra</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>Tiêu chí đánh giá</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>Định mức</t>
+      <c r="A17" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Lịch sử (tiếp)</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>2. Công tác chủ nhiệm &amp; Hoạt động Đoàn thanh niên</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>- Công tác chủ nhiệm lớp; giáo dục truyền thống cách mạng, đạo đức lối sống cho học sinh; phối hợp chặt chẽ với Đoàn thanh niên.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Báo cáo hoạt động giáo dục truyền thống lớp.
+- Học bạ số được phê duyệt đúng hạn.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>1. Kế toán
-(Bậc 1 - 4)</t>
-        </is>
+      <c r="A18" s="7" t="n">
+        <v>15</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Lập dự toán ngân sách, chi trả lương, phụ cấp, BHXH, đối chiếu Kho bạc Nhà nước, quyết toán tài chính quý/năm.</t>
+          <t>Giáo viên môn Lịch sử (tiếp)</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Dự toán được duyệt; bảng lương hàng tháng trước ngày 05; báo cáo tài chính năm đúng luật, không sai sót kiểm toán.</t>
+          <t>3. Sinh hoạt NCBL &amp; Phim tài liệu lịch sử số</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Chính xác tuyệt đối; đúng Luật Ngân sách và Luật Kế toán; 100% đúng thời hạn.</t>
+          <t>- Sinh hoạt chuyên môn theo NCBL; số hóa các thước phim tài liệu lịch sử.
+- Ứng dụng CNTT và AI xây dựng bài giảng lịch sử trực quan, sinh động.</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>40 giờ/tuần
-(01 người)</t>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>- Kho tư liệu phim/hình ảnh lịch sử số hóa.
+- Phiếu đánh giá dự giờ đồng nghiệp.
+- Bài giảng trình chiếu đa phương tiện.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>2. Văn thư
-(Bậc 1 - 4)</t>
-        </is>
+      <c r="A19" s="7" t="n">
+        <v>16</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Xử lý công văn đi đến trên iOffice, quản lý con dấu nhà trường, lập hồ sơ lưu trữ hiện hành và lịch sử, cấp giấy giới thiệu.</t>
+          <t>Giáo viên môn Lịch sử (tiếp)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>100% công văn xử lý trong ngày; bảo quản con dấu an toàn tuyệt đối; số hóa hồ sơ văn bản khoa học.</t>
+          <t>4. Bồi dưỡng HSG Lịch sử &amp; Ôn thi tốt nghiệp KHXH</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Bảo mật, kịp thời, đúng thể thức văn bản theo Nghị định 30/2020/NĐ-CP.</t>
+          <t>- Bồi dưỡng đội tuyển HSG Lịch sử dự thi cấp tỉnh; phụ đạo học sinh yếu.
+- Tổ chức ôn thi tốt nghiệp THPT môn Lịch sử khối KHXH đạt kết quả xuất sắc.</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>40 giờ/tuần
-(01 người)</t>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>- Chuyên đề bồi dưỡng HSG Lịch sử.
+- Học sinh đạt giải HSG môn Lịch sử cấp tỉnh.
+- 100% học sinh đỗ tốt nghiệp môn Lịch sử.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>3. Thiết bị TN
-(Bậc 2 - 3)</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Quản lý thiết bị dạy học, hóa chất phòng thực hành Lý-Hóa-Sinh; chuẩn bị đồ dùng tiết thực hành; an toàn PCCC phòng thí nghiệm.</t>
+      <c r="A20" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Giáo dục thể chất (GDTC)
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 02 biên chế
+Định mức: 17 tiết/tuần</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>100% tiết thực hành có thiết bị chuẩn bị sẵn sàng; sổ theo dõi mượn trả cập nhật hàng tuần; không có tai nạn cháy nổ.</t>
+          <t>1. Giảng dạy môn GDTC &amp; Rèn luyện thể lực</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Bảo quản tốt 100% tài sản; an toàn tuyệt đối phòng thí nghiệm.</t>
+          <t>- Giảng dạy GDTC theo CT 2018 (Điền kinh, Bóng chuyền, Bóng đá, Cầu lông, Thể dục nhịp điệu) đủ 17 tiết/tuần.
+- Rèn luyện tố chất thể lực nhanh, mạnh, bền, khéo léo; bảo đảm an toàn tuyệt đối trong giờ học ngoài trời.</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>40 giờ/tuần
-(01 người)</t>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy GDTC chuẩn bị kỹ lưỡng.
+- Bảng kiểm tra đánh giá tiêu chuẩn rèn luyện thể lực học sinh.
+- 100% tiết dạy an toàn thể lực.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>4. Giáo vụ
-(Bậc 2 - 3)</t>
-        </is>
+      <c r="A21" s="7" t="n">
+        <v>18</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Quản lý sổ đăng bộ, hồ sơ tuyển sinh lớp 10, hồ sơ thi tốt nghiệp THPT, cơ sở dữ liệu học sinh, cấp phát văn bằng chứng chỉ.</t>
+          <t>Giáo viên môn Giáo dục thể chất (GDTC) (tiếp)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Sổ đăng bộ chuẩn xác 100%; hồ sơ tuyển sinh và thi tốt nghiệp nộp về Sở GD&amp;ĐT đúng thời hạn; cấp bằng không sai sót.</t>
+          <t>2. Chủ nhiệm lớp &amp; Thể dục giữa giờ toàn trường</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Chính xác, bảo mật dữ liệu học sinh, tuân thủ quy chế quản lý văn bằng.</t>
+          <t>- Công tác chủ nhiệm lớp; rèn nề nếp kỷ luật, tác phong nhanh nhẹn cho học sinh.
+- Phụ trách duy trì tập thể dục giữa giờ và phong trào thể thao toàn trường.</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>40 giờ/tuần
-(01 người)</t>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Sổ theo dõi nề nếp tập luyện thể dục.
+- Học bạ số ký duyệt đúng hạn.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>5. Y tế trường học
-(Bậc 1 - 3)</t>
-        </is>
+      <c r="A22" s="7" t="n">
+        <v>19</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Sơ cấp cứu tai nạn thương tích; quản lý tủ thuốc; khám sức khỏe định kỳ; phòng chống dịch bệnh; kiểm tra vệ sinh căng tin.</t>
+          <t>Giáo viên môn Giáo dục thể chất (GDTC) (tiếp)</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Tủ thuốc đủ cơ số cấp cứu; 100% học sinh được theo dõi sức khỏe; không để xảy ra dịch bệnh bùng phát hay ngộ độc.</t>
+          <t>3. Sinh hoạt NCBL &amp; Huấn luyện thể thao số</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Kịp thời, chu đáo, tuân thủ quy chuẩn y tế học đường.</t>
+          <t>- Sinh hoạt chuyên môn tổ; tự học nâng cao phương pháp huấn luyện thể thao trường học.
+- Ứng dụng công nghệ phân tích kỹ thuật động tác qua video quay chậm.</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>40 giờ/tuần
-(01 người)</t>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>- Phiếu dự giờ đồng nghiệp.
+- Kế hoạch huấn luyện thể thao trường học.
+- Sáng kiến cải tiến dụng cụ tập luyện.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>6. Thủ quỹ
-(Bậc 1 - 3)</t>
-        </is>
+      <c r="A23" s="7" t="n">
+        <v>20</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Quản lý két quỹ tiền mặt; thực hiện thu và chi tiền mặt đúng phiếu thu/chi có chữ ký Hiệu trưởng &amp; Kế toán; ghi sổ quỹ hàng ngày.</t>
+          <t>Giáo viên môn Giáo dục thể chất (GDTC) (tiếp)</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Số dư quỹ tiền mặt thực tế khớp 100% với sổ quỹ và sổ kế toán; thanh toán tiền mặt kịp thời, an toàn tuyệt đối.</t>
+          <t>4. Huấn luyện HKPĐ &amp; Bảo quản sân bãi TDTT</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Tuyệt đối trung thực, cẩn trọng; khớp số dư 100%; không để xảy ra thiếu hụt.</t>
+          <t>- Huấn luyện đội tuyển học sinh tham gia Hội khỏe Phù Đổng cấp huyện, cấp tỉnh.
+- Quản lý sân bóng đá, sân bóng chuyền, đường chạy và dụng cụ thể thao nhà trường.</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>40 giờ/tuần
-(01 người)</t>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>- Đội tuyển đạt giải/huy chương HKPĐ cấp tỉnh.
+- Biên bản kiểm kê dụng cụ TDTT trường học.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>VI. KHUNG NĂNG LỰC CHO 06 VỊ TRÍ HỖ TRỢ</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="n"/>
-      <c r="C24" s="18" t="n"/>
-      <c r="D24" s="18" t="n"/>
-      <c r="E24" s="18" t="n"/>
+      <c r="A24" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Giáo viên môn GDQP-AN
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 01 biên chế
+Định mức: 17 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>1. Giảng dạy môn GDQP-AN &amp; Kỹ thuật quân sự</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy GDQP-AN 10, 11, 12 (Đường lối quân sự của Đảng, Điều lệnh đội ngũ, Bắn súng tiểu liên AK, Băng bó cứu thương, Chiến thuật bộ binh) định mức 17 tiết/tuần.
+- Giáo dục ý thức bảo vệ chủ quyền biên giới quốc gia tại huyện biên giới Phục Hòa.</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy GDQP-AN đầy đủ.
+- Bảng điểm đánh giá năng lực QP-AN học sinh.
+- 100% tiết thực hành bắn súng laser an toàn tuyệt đối.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>- Năng lực chung: Đạo đức công vụ liêm chính (Cấp độ 3-4); Kỷ luật trách nhiệm (Cấp độ 3-4); Giao tiếp lịch thiệp, phục vụ chu đáo (Cấp độ 3); Ứng dụng công nghệ thông tin và phần mềm chuyên môn (Cấp độ 2-3).
-- Năng lực chuyên môn: Nắm vững quy trình nghiệp vụ tài chính kế toán, văn thư lưu trữ, an toàn thiết bị thí nghiệm, quản lý văn bằng giáo vụ, kỹ năng sơ cứu y tế và nghiệp vụ quản lý quỹ tiền mặt.</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
+      <c r="A25" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn GDQP-AN (tiếp)</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>2. Chủ nhiệm lớp &amp; Nếp sống nội vụ kỷ luật</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>- Công tác chủ nhiệm lớp; rèn luyện nếp sống nội vụ quân sự, tính kỷ luật, tự giác, tinh thần đồng đội cho học sinh.</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Biên bản đánh giá rèn luyện học sinh.
+- Học bạ số hoàn thành đúng hạn.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>VII. MỐI QUAN HỆ CÔNG TÁC</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="n"/>
-      <c r="C26" s="18" t="n"/>
-      <c r="D26" s="18" t="n"/>
-      <c r="E26" s="18" t="n"/>
+      <c r="A26" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn GDQP-AN (tiếp)</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>3. Tập huấn quân sự &amp; Bảo quản vũ khí mô hình</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>- Tham gia tập huấn quân sự của BCH Quân sự tỉnh và Sở GD&amp;ĐT.
+- Bảo quản tủ súng mô hình, trang thiết bị quân trang học đường; ứng dụng mô phỏng 3D bài học quân sự.</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>- Nhật ký bảo quản vũ khí, trang bị mô hình.
+- Phiếu dự giờ đồng nghiệp.
+- Hồ sơ tập huấn QP-AN hàng năm.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>1. Bên trong: Chịu sự quản lý điều hành trực tiếp của Hiệu trưởng và Phó Hiệu trưởng phụ trách; phối hợp chặt chẽ với Tổ chuyên môn, Giáo viên chủ nhiệm, Giáo viên bộ môn.
-2. Bên ngoài: Quan hệ công tác với Kho bạc Nhà nước, Cơ quan Thuế, Trung tâm Y tế huyện, Bảo hiểm xã hội huyện Phục Hòa.</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
+      <c r="A27" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn GDQP-AN (tiếp)</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>4. Huấn luyện Hội thao GDQP-AN cấp tỉnh</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>- Huấn luyện đội tuyển học sinh tham gia Hội thao GDQP-AN cấp tỉnh.
+- Tổ chức các buổi học tập trải nghiệm tại đồn biên phòng, bảo vệ đường biên mốc giới.</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>- Đội tuyển đạt giải Hội thao GDQP-AN cấp tỉnh.
+- Chương trình trải nghiệm biên cương thực tế.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>VIII. PHẠM VI QUYỀN HẠN</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="n"/>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="n"/>
+      <c r="A28" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Địa lí
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 02 biên chế
+Định mức: 17 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>1. Giảng dạy môn Địa lí &amp; Kỹ năng Atlat, GIS</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy Địa lí 10, 11, 12 (Địa lí tự nhiên, Địa lí kinh tế - xã hội thế giới và Việt Nam) định mức 17 tiết/tuần.
+- Rèn kỹ năng đọc bản đồ, biểu đồ, Atlat Địa lí Việt Nam; khai thác kinh tế cửa khẩu Phục Hòa; giáo dục bảo vệ môi trường, biến đổi khí hậu.</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy Địa lí chuẩn quy chế.
+- Hệ thống câu hỏi khai thác Atlat thực hành.
+- Đề kiểm tra định kỳ có bản đặc tả.
+- Tỷ lệ HS đạt chuẩn môn Địa lí ≥ 98%.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>1. Về chuyên môn: Được từ chối các khoản thu - chi hoặc xuất kho thiết bị không đúng quy định, không đủ chứng từ hợp lệ; kiến nghị các biện pháp bảo đảm an toàn trường học.
-2. Về quản lý &amp; Tài chính: Trực tiếp quản lý hệ thống sổ sách, con dấu, cơ sở dữ liệu và tài sản được phân công quản lý.</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
+      <c r="A29" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Địa lí (tiếp)</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>2. Chủ nhiệm lớp &amp; Phong trào trường học xanh</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>- Công tác chủ nhiệm; giáo dục tinh thần bảo vệ môi trường, phân loại rác thải và giữ gìn trường lớp xanh - sạch - đẹp.</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Sổ theo dõi lớp chủ nhiệm.
+- Học bạ số hoàn thành đúng tiến độ.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>IX. YÊU CẦU VỀ TRÌNH ĐỘ, KINH NGHIỆM CHO 06 VỊ TRÍ</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="n"/>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="18" t="n"/>
-      <c r="E30" s="18" t="n"/>
+      <c r="A30" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Địa lí (tiếp)</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>3. Sinh hoạt NCBL &amp; Google Earth, Bản đồ số</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>- Sinh hoạt chuyên môn theo NCBL; khai thác phần mềm Google Earth, hệ thống thông tin địa lý GIS.
+- Ứng dụng AI cập nhật số liệu kinh tế xã hội mới nhất.</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>- Kho học liệu số bản đồ tương tác.
+- Phiếu dự giờ đồng nghiệp.
+- Chuyên đề đổi mới PPDH Địa lí.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>- Kế toán: Đại học chuyên ngành Tài chính - Kế toán; chứng chỉ kế toán viên; làm chủ phần mềm MISA Mimosa.
-- Văn thư: Trung cấp trở lên ngành Văn thư - Lưu trữ; thành thạo hệ thống iOffice và chứng thư số.
-- Thiết bị TN: Cao đẳng trở lên ngành Thiết bị trường học hoặc Lý, Hóa, Sinh; chứng chỉ an toàn hóa chất.
-- Giáo vụ: Trung cấp trở lên ngành Quản lý giáo dục, Tin học hoặc tương đương; thành thạo CSDL ngành GDĐT.
-- Y tế học đường: Trung cấp Y sĩ hoặc Điều dưỡng trở lên; chứng chỉ sơ cấp cứu ban đầu.
-- Thủ quỹ: Trung cấp trở lên ngành Tài chính - Kế toán, Ngân hàng hoặc Kinh tế; phẩm chất đạo đức trung thực tuyệt đối.</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-    </row>
-    <row r="32"/>
+      <c r="A31" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Địa lí (tiếp)</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>4. Bồi dưỡng HSG Địa lí &amp; Ôn thi tốt nghiệp</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>- Bồi dưỡng đội tuyển HSG Địa lí cấp tỉnh; ôn tập thi tốt nghiệp THPT môn Địa lí đạt kết quả cao.</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>- Giáo án bồi dưỡng HSG Địa lí.
+- Học sinh đạt giải HSG môn Địa lí cấp tỉnh.
+- Tỷ lệ đỗ tốt nghiệp môn Địa lí đạt 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Giáo viên môn GD KT&amp;PL
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 01 biên chế
+Định mức: 17 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>1. Giảng dạy GD KT&amp;PL &amp; Tình huống thực tiễn</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy GD KT&amp;PL 10, 11, 12 (Kinh tế, Thị trường, Ngân sách nhà nước, Hệ thống pháp luật Việt Nam) định mức 17 tiết/tuần.
+- Rèn kỹ năng xử lý tình huống pháp luật đời sống, quản lý tài chính cá nhân; giáo dục công dân sống và làm việc theo Hiến pháp và pháp luật.</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy tình huống thực tiễn.
+- Đề kiểm tra đánh giá năng lực pháp luật.
+- Sổ điểm điện tử cập nhật đúng hạn.
+- Tỷ lệ HS đạt chuẩn môn học ≥ 98%.</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>NGƯỜI LẬP BIỂU
-(Ký và ghi rõ họ tên)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>Phục Hòa, ngày .... tháng .... năm 2026
-HIỆU TRƯỞNG
-(Ký tên, đóng dấu)</t>
+      <c r="A33" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn GD KT&amp;PL (tiếp)</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>2. Chủ nhiệm &amp; Tuyên truyền an toàn pháp luật</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>- Công tác chủ nhiệm lớp; tuyên truyền phổ biến giáo dục pháp luật ATGT, phòng chống bạo lực học đường, tệ nạn xã hội trong nhà trường.</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Hồ sơ tuyên truyền phổ biến pháp luật.
+- Học bạ số được phê duyệt đúng kỳ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn GD KT&amp;PL (tiếp)</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>3. Sinh hoạt NCBL &amp; Trợ lý AI pháp luật học đường</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>- Sinh hoạt chuyên môn theo NCBL; cập nhật các luật mới ban hành của Quốc hội.
+- Ứng dụng AI phân tích tình huống pháp luật thực tế cho học sinh.</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>- Bộ tư liệu tình huống pháp luật số hóa.
+- Phiếu dự giờ đồng nghiệp.
+- Chuyên đề giáo dục pháp luật học đường.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn GD KT&amp;PL (tiếp)</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>4. Bồi dưỡng HSG KT&amp;PL &amp; Ôn thi tốt nghiệp</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>- Bồi dưỡng đội tuyển HSG môn GD KT&amp;PL thi cấp tỉnh; phụ đạo học sinh ôn thi tốt nghiệp THPT tổ hợp KHXH.</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>- Chuyên đề bồi dưỡng HSG KT&amp;PL.
+- Học sinh đạt giải HSG cấp tỉnh môn KT&amp;PL.
+- Tỷ lệ học sinh đỗ tốt nghiệp môn học đạt 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Vật lí
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 01 biên chế
+Định mức: 17 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>1. Giảng dạy môn Vật lí, Phòng thí nghiệm &amp; STEM</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy môn Vật lí 10, 11, 12 (Cơ học, Nhiệt học, Điện từ học, Quang học, Hạt nhân) định mức 17 tiết/tuần.
+- Thực hiện đầy đủ các tiết thí nghiệm thực hành tại phòng bộ môn; thiết kế các bài học STEM Vật lí ứng dụng thực tiễn; ôn thi TN THPT KHTN.</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy môn Vật lí tích hợp thí nghiệm.
+- Kế hoạch bài dạy STEM được phê duyệt.
+- Đề thi trắc nghiệm theo ma trận mới.
+- 100% tiết thực hành bảo đảm an toàn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Vật lí (tiếp)</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>2. Chủ nhiệm lớp &amp; Hướng nghiệp khối Kỹ thuật</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>- Công tác chủ nhiệm lớp; quản lý nề nếp học tập, rèn luyện kỹ năng sống và tư vấn hướng nghiệp khối ngành kỹ thuật công nghệ cho học sinh.</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Biên bản sinh hoạt lớp hàng tuần.
+- Học bạ điện tử nhận xét và ký số đúng hạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Vật lí (tiếp)</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>3. Sinh hoạt NCBL, Thí nghiệm ảo PhET &amp; AI</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>- Sinh hoạt tổ chuyên môn; bảo quản thiết bị bộ môn Vật lí.
+- Sử dụng phần mềm mô phỏng thí nghiệm ảo PhET; ứng dụng AI tạo câu hỏi trắc nghiệm vật lí định tính và định lượng.</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>- Kho bài giảng thí nghiệm ảo Vật lí.
+- Phiếu dự giờ đồng nghiệp.
+- Sáng kiến kinh nghiệm cấp cơ sở.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Vật lí (tiếp)</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>4. Bồi dưỡng HSG Vật lí, NCKH &amp; Ôn thi TN</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>- Bồi dưỡng đội tuyển HSG môn Vật lí cấp tỉnh; hướng dẫn học sinh nghiên cứu KHKT dành cho học sinh trung học; ôn thi TN THPT môn Vật lí.</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>- Học sinh đạt giải HSG môn Vật lí cấp tỉnh.
+- Dự án KHKT/STEM tham gia cấp tỉnh.
+- Phổ điểm tốt nghiệp môn Vật lí đạt cao.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Hóa học
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 01 biên chế
+Định mức: 17 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>1. Giảng dạy môn Hóa học &amp; Thực hành phòng Lab</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy Hóa học 10, 11, 12 (Cấu tạo nguyên tử, Bảng tuần hoàn, Liên kết hóa học, Nhiệt hóa học, Vô cơ và Hữu cơ) định mức 17 tiết/tuần.
+- Hướng dẫn thực hành thí nghiệm an toàn tuyệt đối; sử dụng phần mềm ChemDraw vẽ cấu tạo phân tử; giáo dục bảo vệ môi trường chống ô nhiễm hóa chất.</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy Hóa học gắn thực nghiệm.
+- Báo cáo kết quả thực hành thí nghiệm học sinh.
+- Đề kiểm tra định kỳ có ma trận chuẩn.
+- Tỷ lệ HS đạt chuẩn môn Hóa ≥ 96%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Hóa học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>2. Chủ nhiệm lớp &amp; Hướng nghiệp khối Y Dược</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>- Công tác chủ nhiệm lớp; định hướng nghề nghiệp khối ngành Y - Dược, Hóa thực phẩm, Nông nghiệp sạch; quản lý học sinh toàn diện.</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Hồ sơ theo dõi học sinh lớp chủ nhiệm.
+- Học bạ số ký duyệt đúng kỳ hạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Hóa học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>3. Sinh hoạt NCBL &amp; An toàn hóa chất phòng Lab</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>- Sinh hoạt chuyên môn theo NCBL; quản lý hóa chất, tủ hút phòng bộ môn; phối hợp nhân viên thiết bị thí nghiệm; ứng dụng AI tra cứu phản ứng hóa học.</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>- Phiếu dự giờ đồng nghiệp.
+- Sổ an toàn phòng thí nghiệm Hóa học.
+- Bài giảng tương tác mô hình 3D phân tử.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Hóa học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>4. Bồi dưỡng HSG Hóa học &amp; Ôn thi tốt nghiệp</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>- Bồi dưỡng đội tuyển HSG môn Hóa học cấp tỉnh; ôn thi tốt nghiệp THPT môn Hóa đạt phổ điểm cao; phụ đạo học sinh yếu môn Hóa.</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>- Học sinh đạt giải HSG môn Hóa cấp tỉnh.
+- Kết quả tốt nghiệp môn Hóa đạt chỉ tiêu giao.
+- Chuyên đề bồi dưỡng HSG Hóa học.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Sinh học
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 01 biên chế
+Định mức: 17 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>1. Giảng dạy môn Sinh học &amp; Tiêu bản hiển vi</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy Sinh học 10, 11, 12 (Tế bào, Vi sinh vật, Sinh học cơ thể, Di truyền, Sinh thái) định mức 17 tiết/tuần.
+- Hướng dẫn học sinh thao tác sử dụng kính hiển vi quang học, làm tiêu bản hiển vi; giáo dục sức khỏe sinh sản, bảo tồn đa dạng sinh học rừng Cao Bằng.</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy Sinh học thực nghiệm.
+- Báo cáo thực hành kính hiển vi của học sinh.
+- Đề kiểm tra định kỳ có ma trận chuẩn.
+- Tỷ lệ HS đạt chuẩn môn Sinh ≥ 97%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Sinh học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>2. Chủ nhiệm lớp &amp; Chăm sóc vườn sinh thái</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>- Công tác chủ nhiệm; xây dựng phong trào chăm sóc vườn hoa cây cảnh, bảo vệ môi trường sinh thái trường học xanh sạch đẹp; quản lý nề nếp học sinh.</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Sổ theo dõi nề nếp học sinh.
+- Học bạ số được ký số chuẩn quy chế.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Sinh học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>3. Sinh hoạt NCBL &amp; Mô hình 3D Sinh học số</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>- Sinh hoạt chuyên môn theo NCBL; xây dựng mô hình sinh thái thực nghiệm.
+- Ứng dụng công cụ AI phân tích quy luật di truyền và tra cứu cơ sở dữ liệu sinh học.</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>- Kho học liệu hình ảnh, video sinh học tế bào.
+- Phiếu dự giờ đồng nghiệp.
+- Chuyên đề đổi mới PPDH môn Sinh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Sinh học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>4. Bồi dưỡng HSG Sinh học &amp; Ôn thi tốt nghiệp</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>- Bồi dưỡng đội tuyển HSG môn Sinh học thi cấp tỉnh; hướng dẫn học sinh đề tài KHKT thuộc lĩnh vực Y - Sinh học; ôn thi TN THPT khối KHTN.</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>- Học sinh đạt giải HSG Sinh học cấp tỉnh.
+- Dự án NCKH học sinh tham gia cấp tỉnh.
+- Tỷ lệ học sinh đỗ tốt nghiệp môn Sinh đạt 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Công nghệ
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 02 biên chế
+Định mức: 17 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>1. Giảng dạy môn Công nghệ (Công nghiệp &amp; Nông nghiệp)</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy Công nghệ định hướng Công nghiệp (Bản vẽ, Cơ khí, Điện) và Nông nghiệp công nghệ cao (Trồng trọt, Chăn nuôi, Thủy sản sạch) định mức 17 tiết/tuần.
+- Hướng dẫn thực hành an toàn điện và mô hình nông nghiệp thích ứng khí hậu vùng núi Phục Hòa.</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy Công nghệ gắn thực tiễn.
+- Sản phẩm thực hành mạch điện của học sinh.
+- Báo cáo dự án nông nghiệp công nghệ cao.
+- Tỷ lệ HS đạt chuẩn môn Công nghệ ≥ 98%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Công nghệ (tiếp)</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>2. Chủ nhiệm lớp &amp; Phân luồng đào tạo nghề</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>- Công tác chủ nhiệm lớp; giáo dục hướng nghiệp, phân luồng học sinh sau THPT tiếp cận học nghề kỹ thuật công nghiệp hoặc đại học công nghệ.</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Hồ sơ tư vấn hướng nghiệp học sinh.
+- Học bạ số hoàn thành đúng hạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Công nghệ (tiếp)</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>3. Sinh hoạt NCBL &amp; Mô phỏng mạch điện AutoCAD</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>- Sinh hoạt tổ chuyên môn; khai thác phần mềm AutoCAD, mô phỏng mạch điện.
+- Ứng dụng AI tìm kiếm ý tưởng thiết kế sản phẩm STEM công nghệ tiện ích.</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>- Kho học liệu số mô hình kỹ thuật 3D.
+- Phiếu dự giờ đồng nghiệp.
+- Sản phẩm sáng tạo kỹ thuật của giáo viên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Công nghệ (tiếp)</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>4. Sáng tạo KHKT &amp; Ngày hội STEM trường học</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>- Hướng dẫn học sinh tham gia cuộc thi Sáng tạo thanh thiếu niên nhi đồng và KHKT cấp tỉnh.
+- Nòng cốt tổ chức Ngày hội STEM trường học; phụ đạo học sinh.</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>- Sản phẩm/mô hình đạt giải Sáng tạo KHKT cấp tỉnh.
+- Kế hoạch và sản phẩm Ngày hội STEM trường học.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Tin học
+(GV-THPT-01)
+Bậc 3 đến Bậc 4 | 01 biên chế
+Định mức: 17 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>1. Giảng dạy Tin học, Lập trình Python &amp; Quản trị phòng máy</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy Tin học 10, 11, 12 theo CT 2018 (Khoa học máy tính &amp; Tin học ứng dụng: Python, CSDL số, Mạng, An ninh mạng, AI) định mức 17 tiết/tuần.
+- Quản lý bảo đảm 02 phòng máy vi tính vận hành ổn định phục vụ thực hành cho toàn trường.</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bài dạy Tin học lập trình Python.
+- Bài tập dự án phần mềm của học sinh.
+- Đề thi thực hành trên máy tính chấm tự động.
+- Hệ thống phòng máy vi tính hoạt động 99.9%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Tin học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>2. Chủ nhiệm lớp &amp; Văn hóa an toàn không gian mạng</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>- Công tác chủ nhiệm lớp; giáo dục văn hóa ứng xử trên không gian mạng, phòng chống lừa đảo trực tuyến và bảo vệ dữ liệu cá nhân cho học sinh.</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch chủ nhiệm năm học.
+- Biên bản sinh hoạt chuyên đề an toàn mạng.
+- Học bạ số ký duyệt đúng thời hạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Tin học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>3. Nòng cốt CĐS &amp; Tập huấn AI toàn trường</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>- Quản trị kỹ thuật mạng LAN, máy chủ nhà trường.
+- Tập huấn hướng dẫn cán bộ giáo viên sử dụng phần mềm dạy học số và các công cụ AI (Gemini, ChatGPT) trong soạn giảng.</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>- Nhật ký bảo trì hệ thống mạng &amp; phòng máy.
+- Tài liệu tập huấn ứng dụng AI cho giáo viên.
+- Phiếu dự giờ đồng nghiệp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên môn Tin học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>4. Bồi dưỡng HSG Tin học &amp; Hỗ trợ thi trực tuyến</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>- Bồi dưỡng đội tuyển HSG Tin học lập trình dự thi cấp tỉnh.
+- Trực kỹ thuật các kỳ thi khảo sát trực tuyến, thi nghề số hóa của nhà trường.</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>- Đội tuyển HSG Tin học đạt giải cấp tỉnh.
+- Hệ thống thi trực tuyến thông suốt 100%.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C10:E10"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3071,77 +4128,954 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="68" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>DANH MỤC 3: BẢN MÔ TẢ VỊ TRÍ VIỆC LÀM VIÊN CHỨC HỖ TRỢ (06 NGƯỜI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Vị trí việc làm &amp; Mã số</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Nhiệm vụ quản lý chính</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>Nội dung công việc cụ thể &amp; Tiêu chí đo lường</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>Tỷ trọng</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Sản phẩm / Kết quả đầu ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Kế toán viên
+(KT-THPT-01)
+Bậc 1 đến Bậc 4 | 01 biên chế
+Định mức: 40 giờ/tuần</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>1. Quản lý dự toán, ngân sách &amp; Báo cáo tài chính</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>- Quản lý tài chính, ngân sách nhà nước và các nguồn thu hợp pháp; lập dự toán ngân sách hàng năm.
+- Thực hiện thanh quyết toán qua Kho bạc Nhà nước; lập báo cáo tài chính quý/năm theo Luật Kế toán; lưu trữ chứng từ kế toán an toàn, bảo mật.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>- Dự toán ngân sách năm học được duyệt.
+- Báo cáo quyết toán tài chính quý/năm được Sở GD&amp;ĐT phê chuẩn.
+- Sổ cái, sổ chi tiết các tài khoản kế toán.
+- 100% hồ sơ thanh toán Kho bạc không bị từ chối.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Kế toán viên (tiếp)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>2. Tiền lương, phụ cấp, BHXH &amp; Chế độ học sinh</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>- Tính toán chi trả tiền lương, phụ cấp ưu đãi nghề, phụ cấp thâm niên, BHXH, BHYT, chế độ thừa giờ cho cán bộ giáo viên đúng hạn.
+- Chi trả chế độ chính sách miễn giảm học phí, hỗ trợ chi phí học tập cho học sinh vùng đặc biệt khó khăn kịp thời, chính xác.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>- Bảng thanh toán lương chuyển khoản trước ngày 05 hàng tháng.
+- Hồ sơ giải quyết chế độ chính sách học sinh đúng đối tượng, đủ định mức.
+- Chứng từ chi trả chế độ lưu trữ đúng quy định.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Văn thư trường học
+(VT-THPT-01)
+Bậc 1 đến Bậc 4 | 01 biên chế
+Định mức: 40 giờ/tuần</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>1. Quản lý văn bản điện tử, công văn đi - đến</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>- Quản lý hệ thống văn bản đi - đến trên phần mềm Quản lý văn bản điện tử và điều hành (iOffice).
+- Tiếp nhận, vào sổ, chuyển giao công văn trong ngày làm việc.
+- Rà soát thể thức văn bản hành chính theo Nghị định 30/2020/NĐ-CP trước khi trình ký; phát hành văn bản điện tử ký số đúng quy trình.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>- Sổ đăng ký văn bản đi / đến điện tử cập nhật 100%.
+- 100% công văn đến được chuyển giao kịp thời trong ngày.
+- Văn bản phát hành bảo đảm đúng thể thức và kỹ thuật trình bày.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Văn thư trường học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>2. Quản lý con dấu, chứng thư số &amp; Lưu trữ hồ sơ</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>- Quản lý, sử dụng và bảo quản con dấu của trường THPT Phục Hòa và thiết bị lưu khóa bí mật (chứng thư số) an toàn tuyệt đối.
+- Lập danh mục hồ sơ cơ quan, thu thập và lập hồ sơ tài liệu lưu trữ hiện hành; phục vụ tra cứu tài liệu lưu trữ nhanh chóng, chính xác.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>- Sổ theo dõi đóng dấu và sử dụng chứng thư số.
+- Danh mục hồ sơ lưu trữ năm học chuẩn quy chế.
+- Không để xảy ra thất lạc tài liệu hoặc sử dụng con dấu sai quy định.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Thiết bị, thí nghiệm
+(TBTN-THPT-01)
+Bậc 2 đến Bậc 3 | 01 biên chế
+Định mức: 40 giờ/tuần</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>1. Quản lý thiết bị dạy học &amp; Chuẩn bị phòng thực hành</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>- Quản lý, bảo quản toàn bộ trang thiết bị dạy học, đồ dùng dạy học, mô hình, hóa chất tại các phòng thực hành Vật lí, Hóa học, Sinh học, Công nghệ.
+- Chuẩn bị đầy đủ thiết bị, dụng cụ, hóa chất thí nghiệm trước các tiết dạy thực hành của giáo viên theo lịch báo giảng; hướng dẫn quy định an toàn phòng thí nghiệm.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>- Sổ theo dõi sử dụng phòng học bộ môn &amp; mượn trả thiết bị dạy học.
+- 100% tiết thực hành có thiết bị chuẩn bị sẵn sàng trước giờ học.
+- Tuyệt đối an toàn cháy nổ, không để xảy ra sự cố phòng thí nghiệm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Thiết bị, thí nghiệm (tiếp)</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>2. Kiểm kê, bảo dưỡng &amp; Đề xuất mua sắm bổ sung</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>- Kiểm kê thiết bị dạy học định kỳ cuối học kỳ và năm học; lập hồ sơ đề xuất thanh lý thiết bị hỏng không thể khắc phục.
+- Lập dự trù đề xuất mua sắm bổ sung hóa chất, dụng cụ thực hành tiêu hao đầu năm học mới; vệ sinh, bảo dưỡng trang thiết bị máy móc thường xuyên.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>- Biên bản kiểm kê tài sản thiết bị dạy học cuối năm.
+- Danh mục đề xuất mua sắm bổ sung TBDH được phê duyệt.
+- Sổ nhật ký bảo dưỡng thiết bị dạy học ghi chép định kỳ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Giáo vụ trường học
+(GVU-THPT-01)
+Bậc 2 đến Bậc 3 | 01 biên chế
+Định mức: 40 giờ/tuần</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>1. Quản lý sổ đăng bộ, hồ sơ học sinh &amp; CSDL ngành</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>- Quản lý sổ đăng bộ của nhà trường; quản lý và lưu trữ hồ sơ tuyển sinh vào lớp 10, hồ sơ học sinh chuyển trường đi - chuyển trường đến, hồ sơ học sinh thôi học.
+- Quản lý cơ sở dữ liệu học sinh trên hệ thống CSDL ngành; kiểm tra tính hợp lệ và đồng bộ dữ liệu học bạ số của các khối lớp.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>- Sổ đăng bộ trường THPT số hóa chính xác 100%.
+- Hồ sơ tuyển sinh lớp 10 được phê duyệt đầy đủ.
+- Cơ sở dữ liệu ngành cập nhật đầy đủ, không sai sót thông tin học sinh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Giáo vụ trường học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>2. Phục vụ kỳ thi TN THPT &amp; Quản lý cấp phát văn bằng</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>- Phối hợp tổ chức kỳ thi tốt nghiệp THPT, kỳ thi chọn học sinh giỏi cấp tỉnh và các kỳ kiểm tra chung của trường (lập danh sách thí sinh, đánh số báo danh, chuẩn bị thẻ dự thi, hồ sơ phòng thi).
+- Quản lý sổ cấp phát bằng tốt nghiệp THPT, học bạ và giấy chứng nhận tốt nghiệp tạm thời cho học sinh.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>- Hồ sơ đăng ký dự thi tốt nghiệp THPT nộp Sở GD&amp;ĐT đúng thời hạn.
+- Sổ cấp phát văn bằng, chứng chỉ có đầy đủ chữ ký người nhận.
+- Cấp phát bằng tốt nghiệp kịp thời, chính xác 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Y tế trường học
+(YT-THPT-01)
+Bậc 1 đến Bậc 3 | 01 biên chế
+Định mức: 40 giờ/tuần</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1. Chăm sóc sức khỏe ban đầu, sơ cấp cứu &amp; Tủ thuốc</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>- Chăm sóc sức khỏe ban đầu, sơ cứu và cấp cứu kịp thời các tai nạn thương tích hoặc ốm đau đột xuất của học sinh và CBGVNV.
+- Quản lý tủ thuốc y tế học đường, dự trù cơ số thuốc thiết yếu, bông băng, dụng cụ y tế; lập và quản lý hồ sơ theo dõi sức khỏe từng học sinh qua các năm học.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>- Sổ theo dõi khám chữa bệnh và cấp phát thuốc.
+- Sổ theo dõi sức khỏe định kỳ học sinh.
+- Tủ thuốc y tế có đầy đủ thuốc sơ cứu còn hạn sử dụng.
+- 100% ca sơ cứu học đường được xử lý kịp thời, an toàn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Y tế trường học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>2. Khám sức khỏe định kỳ, phòng dịch &amp; BHYT học sinh</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>- Phối hợp với Trung tâm Y tế huyện Phục Hòa tổ chức khám sức khỏe định kỳ cho học sinh đầu năm học.
+- Triển khai công tác phòng chống dịch bệnh truyền nhiễm trong trường học (sốt xuất huyết, cúm, Covid...).
+- Kiểm tra điều kiện vệ sinh học đường, nguồn nước uống và an toàn thực phẩm; tuyên truyền bảo hiểm y tế học sinh đạt 100%.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>- Báo cáo kết quả khám sức khỏe học sinh toàn trường.
+- Kế hoạch và biên bản kiểm tra vệ sinh an toàn thực phẩm, nước uống.
+- 100% học sinh tham gia BHYT học sinh; không xảy ra dịch bệnh học đường.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Thủ quỹ trường học
+(TQ-THPT-01)
+Bậc 1 đến Bậc 3 | 01 biên chế
+Định mức: 40 giờ/tuần</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>1. Quản lý két sắt, quỹ tiền mặt &amp; Thu - chi đúng phiếu</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>- Trực tiếp quản lý quỹ tiền mặt tại két sắt của nhà trường; bảo đảm an toàn tuyệt đối tiền mặt trong mọi tình huống.
+- Thực hiện nghiêm ngặt nguyên tắc tài chính: chỉ thu tiền hoặc xuất tiền khi có Phiếu thu, Phiếu chi hợp pháp có đầy đủ chữ ký của Hiệu trưởng (Chủ tài khoản) và Kế toán.
+- Ký nhận và yêu cầu người nhận tiền ký nhận rõ ràng, ghi rõ họ tên trên phiếu chi.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>- 100% phiếu thu, phiếu chi có đầy đủ chữ ký hợp lệ trước khi xuất/nhập quỹ.
+- Quỹ tiền mặt an toàn tuyệt đối, không thất thoát.
+- Tiền mặt được kiểm đếm chính xác, phân loại ngăn nắp trong két sắt chống cháy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Thủ quỹ trường học (tiếp)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>2. Ghi chép sổ quỹ hàng ngày &amp; Đối chiếu khớp số dư</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>- Mở sổ quỹ tiền mặt và ghi chép sổ quỹ hàng ngày theo trình tự thời gian phát sinh nghiệp vụ thu, chi.
+- Định kỳ hàng ngày, tuần, tháng đối chiếu số tồn quỹ thực tế với Kế toán; lập biên bản kiểm kê quỹ tiền mặt đột xuất và định kỳ cuối tháng/quý/năm.
+- Nộp tiền mặt vào tài khoản Kho bạc/Ngân hàng theo đúng quy định quản lý tiền mặt.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>- Sổ quỹ tiền mặt ghi chép rõ ràng, sạch sẽ, cập nhật hàng ngày.
+- Biên bản đối chiếu khớp 100% số dư tiền mặt giữa Thủ quỹ và Kế toán.
+- Biên bản kiểm kê quỹ tiền mặt định kỳ cuối tháng/quý/năm.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>SỞ GIÁO DỤC VÀ ĐÀO TẠO CAO BẰNG
+TRƯỜNG THPT PHỤC HÒA</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM
+Độc lập – Tự do – Hạnh phúc
+_______________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>BẢN MÔ TẢ CÔNG VIỆC VÀ KHUNG NĂNG LỰC VỊ TRÍ VIỆC LÀM VIÊN CHỨC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>(Mẫu chuẩn theo Phần B Phụ lục IV/VI của Nghị định số 232/2026/NĐ-CP ngày 26/6/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>I. THÔNG TIN CHUNG VỀ VỊ TRÍ VIỆC LÀM</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Tên vị trí việc làm</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên trung học phổ thông (Giáo viên 13 môn học trong Phụ lục I) / Viên chức Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Mã số vị trí việc làm</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>GV-THPT-01 (Chuyên môn) | KT, VT, TBTN, GVU, YT, TQ (Hỗ trợ)</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Bậc chức danh nghề nghiệp</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Chuyên môn: Bậc 3 đến Bậc 4 | Hỗ trợ: Bậc 1 đến Bậc 4</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Cơ quan, đơn vị sử dụng</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Trường THPT Phục Hòa, huyện Phục Hòa, tỉnh Cao Bằng</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Vị trí việc làm cấp trên</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Tổ trưởng chuyên môn, Phó Hiệu trưởng, Hiệu trưởng Trường THPT Phục Hòa</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Định mức làm việc</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên: 17 tiết/tuần | Viên chức hỗ trợ: 40 giờ/tuần</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>II. MỤC TIÊU VỊ TRÍ VIỆC LÀM</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Đảm nhận nhiệm vụ giảng dạy và giáo dục học sinh theo Chương trình GDPT 2018 (đối với GV 13 môn học) và bảo đảm các điều kiện về tài chính, văn thư, thiết bị thí nghiệm, giáo vụ, y tế học đường, ngân quỹ phục vụ vận hành thông suốt của nhà trường (đối với 06 viên chức hỗ trợ).</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>III. CÁC CÔNG VIỆC VÀ KẾT QUẢ ĐẦU RA CỤ THỂ</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Chi tiết cụ thể theo từng môn học và từng vị trí hỗ trợ được quy định tại Sheet 3 (Quản lý), Sheet 4 (13 Môn học Chuyên môn) và Sheet 5 (06 Vị trí Hỗ trợ).</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>IV. KHUNG NĂNG LỰC VỊ TRÍ VIỆC LÀM</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>1. Năng lực chung:
+ - Đạo đức nghề nghiệp, liêm chính sư phạm, phục vụ nhân dân (Cấp độ 4 - 5)
+ - Kỷ luật, trách nhiệm và tinh thần hợp tác đồng nghiệp (Cấp độ 4 - 5)
+ - Đổi mới sáng tạo, chuyển đổi số và ứng dụng AI (Cấp độ 3 - 4)
+2. Năng lực chuyên môn nghiệp vụ:
+ - Nắm vững kiến thức bộ môn theo CT GDPT 2018 (Cấp độ 4 - 5)
+ - Kỹ năng sư phạm, tổ chức hoạt động học tập, dạy học STEM (Cấp độ 4 - 5)
+ - Đánh giá năng lực học sinh theo thông tư Bộ GD&amp;ĐT (Cấp độ 4)</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>V. MỐI QUAN HỆ CÔNG TÁC</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>1. Quan hệ bên trong: Báo cáo trực tiếp Tổ trưởng CM, Phó Hiệu trưởng, Hiệu trưởng; phối hợp với GV chủ nhiệm, GV bộ môn, nhân viên Thiết bị, Thư viện, Y tế, Giáo vụ, Thủ quỹ.
+2. Quan hệ bên ngoài: Phối hợp thường xuyên với Cha mẹ học sinh; Hội Khuyến học địa phương; Phòng chuyên môn Sở GD&amp;ĐT Cao Bằng.</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>VI. PHẠM VI QUYỀN HẠN</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>1. Về chuyên môn: Chủ động lựa chọn PPDH, kiểm tra đánh giá theo kế hoạch giáo dục môn học; đánh giá xếp loại học sinh theo quy chế; tham gia biên soạn tài liệu giáo dục địa phương.
+2. Về quản lý: Quản lý học sinh trong giờ học và các hoạt động giáo dục phân công.
+3. Về bảo đảm điều kiện: Được trang bị đầy đủ phương tiện dạy học, phòng thực hành bộ môn, thiết bị CNTT, chế độ phụ cấp và bảo hộ lao động theo quy định.</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>VII. YÊU CẦU VỀ TRÌNH ĐỘ, KINH NGHIỆM, PHẨM CHẤT</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>- Về trình độ đào tạo: Bằng Cử nhân (Đại học) sư phạm trở lên đúng chuyên ngành đối với Giáo viên; Bằng Đại học/Cao đẳng/Trung cấp chuyên ngành phù hợp đối với Viên chức hỗ trợ (Kế toán, Văn thư, Thiết bị, Y tế...).
+- Về chứng chỉ: Có chứng chỉ bồi dưỡng tiêu chuẩn chức danh nghề nghiệp viên chức theo quy định.
+- Về kỹ năng số: Sử dụng thành thạo máy vi tính, phần mềm quản lý giáo dục điện tử, ký số học bạ, khai thác công cụ AI hỗ trợ công việc.
+- Phẩm chất đạo đức: Mẫu mực, tâm huyết với sự nghiệp giáo dục vùng cao Phục Hòa.</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>NGƯỜI LẬP BIỂU
+(Ký và ghi rõ họ tên)</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Phục Hòa, ngày .... tháng .... năm 2026
+HIỆU TRƯỞNG
+(Ký tên, đóng dấu)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="C10:E10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="66" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="68" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>KHUNG NĂNG LỰC TOÀN DIỆN CỦA 03 DANH MỤC VTVL (5 CẤP ĐỘ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>(Căn cứ Điều 8, Điều 9 &amp; Phụ lục IV/VI Nghị định số 232/2026/NĐ-CP - Chuẩn hóa 35 Biên chế)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>KHUNG NĂNG LỰC TOÀN DIỆN CHO 03 NHÓM VỊ TRÍ VIỆC LÀM (5 CẤP ĐỘ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Nhóm năng lực</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>Tên năng lực cụ thể</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>DM1: Quản lý</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>DM2: Chuyên môn (13 môn)</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>DM3: Hỗ trợ (6 VC)</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>Mô tả chuẩn hành vi yêu cầu</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>Nhóm năng lực</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>Tên năng lực thành phần</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>Yêu cầu Nhóm 1
-(07 Quản lý)</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>Yêu cầu Nhóm 2
-(22 GV 13 Môn)</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>Yêu cầu Nhóm 3
-(06 VC Hỗ trợ)</t>
-        </is>
-      </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>Mô tả chuẩn hành vi &amp; Tiêu chí đạt</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Năng lực chung</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Phẩm chất chính trị &amp; Đạo đức nghề nghiệp</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Cấp độ 4 - 5</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Cấp độ 3 - 4</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Cấp độ 2 - 3</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Tuyệt đối trung thành, gương mẫu, giữ gìn phẩm chất nhà giáo, liêm chính.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -3151,34 +5085,34 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Đạo đức nghề nghiệp &amp; Liêm chính sư phạm</t>
+          <t>Giao tiếp, ứng xử &amp; Tinh thần hợp tác</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 5</t>
+          <t>Cấp độ 4 - 5</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 4 - 5</t>
+          <t>Cấp độ 3 - 4</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 3 - 4</t>
+          <t>Cấp độ 2 - 3</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Tuyệt đối gương mẫu, không vụ lợi, chấp hành nghiêm quy tắc ứng xử trường học.</t>
+          <t>Giao tiếp sư phạm chuẩn mực, tôn trọng học sinh, phụ huynh và đồng nghiệp.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -3188,34 +5122,34 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Kỷ luật, trách nhiệm &amp; Tinh thần phụng sự</t>
+          <t>Đổi mới, sáng tạo &amp; Chuyển đổi số</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 5</t>
+          <t>Cấp độ 4 - 5</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 4</t>
+          <t>Cấp độ 3 - 4</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 3 - 4</t>
+          <t>Cấp độ 2 - 3</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Tuân thủ kỷ luật lao động, hoàn thành công việc được giao đúng hạn và chất lượng.</t>
+          <t>Chủ động đề xuất cải tiến quy trình làm việc, ứng dụng CNTT và AI hiệu quả.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -3225,7 +5159,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Kỹ năng giao tiếp, ứng xử &amp; Phối hợp công tác</t>
+          <t>Kỹ năng số, CNTT &amp; Công cụ AI</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -3240,56 +5174,56 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 3</t>
+          <t>Cấp độ 2 - 3</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Ứng xử chuẩn mực với phụ huynh, học sinh, đồng nghiệp; hợp tác hiệu quả.</t>
+          <t>Khai thác thành thạo phần mềm quản lý, ký số học bạ điện tử, công cụ AI.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Năng lực chung</t>
+          <t>Năng lực quản lý</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Ứng dụng CNTT, CĐS &amp; Sử dụng AI</t>
+          <t>Tư duy chiến lược &amp; Lập kế hoạch</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 4</t>
+          <t>Cấp độ 4 - 5</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 3 - 5</t>
+          <t>Cấp độ 2 - 3</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 2 - 3</t>
+          <t>Cấp độ 1 - 2</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Khai thác phần mềm ngành, ký số học bạ, sử dụng AI hỗ trợ công việc chuyên môn.</t>
+          <t>Hoạch định chiến lược phát triển trường, kế hoạch giáo dục tổ chuyên môn.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -3299,7 +5233,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Tư duy chiến lược &amp; Lập kế hoạch</t>
+          <t>Tổ chức điều hành &amp; Kiểm tra giám sát</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -3319,14 +5253,14 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Xây dựng tầm nhìn, phân bổ nguồn lực khoa học, dự báo tình huống quản trị.</t>
+          <t>Phân công nhiệm vụ hợp lý, kiểm tra đánh giá tiến độ và kết quả công việc.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -3336,7 +5270,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Tổ chức điều hành &amp; Kiểm tra giám sát</t>
+          <t>Quản trị nhân lực &amp; Phát triển đội ngũ</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3351,19 +5285,19 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 1 - 2</t>
+          <t>Cấp độ 1</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Phân công nhiệm vụ hợp lý, kiểm tra đôn đốc tiến độ, xử lý công bằng khách quan.</t>
+          <t>Xây dựng khối đoàn kết nội bộ, động viên khích lệ cán bộ giáo viên phát triển.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -3373,7 +5307,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Nghiệp vụ sư phạm môn học / Chuyên môn hỗ trợ</t>
+          <t>Nghiệp vụ sư phạm / Chuyên ngành</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3388,19 +5322,19 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 3 - 4</t>
+          <t>Cấp độ 2 - 3</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Nắm vững kiến thức 13 môn học GDPT 2018 hoặc chuyên ngành tài chính/văn thư/y tế.</t>
+          <t>Nắm vững chuyên môn kiến thức môn học, phương pháp dạy học tích cực, STEM.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -3410,7 +5344,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Phương pháp dạy học tích cực / Kỹ thuật nghiệp vụ</t>
+          <t>Xây dựng kế hoạch dạy học &amp; Bài dạy</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -3420,626 +5354,686 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 4 - 5</t>
+          <t>Cấp độ 3 - 5</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 2 - 3</t>
+          <t>Cấp độ 1 - 2</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Vận dụng PPDH tích cực, giáo dục STEM, kỹ thuật ghi chép và quy trình kiểm soát.</t>
+          <t>Thiết kế giáo án chuẩn CT GDPT 2018, ma trận và đề kiểm tra định kỳ.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Năng lực chuyên môn</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Nghiên cứu khoa học &amp; Bồi dưỡng HSG</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Cấp độ 3 - 4</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Cấp độ 3 - 5</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Cấp độ 1 - 2</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Có sáng kiến kinh nghiệm cấp cơ sở, bồi dưỡng học sinh đạt giải cấp tỉnh.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="63" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>BỘ TIÊU CHÍ KPI ĐO LƯỜNG HIỆU QUẢ CÔNG VIỆC CHO 03 NHÓM VTVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Danh mục VTVL</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Vị trí áp dụng</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Chỉ số KPI chính</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Mục tiêu định lượng</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Tần suất</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Trọng số</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>DM1: Quản lý</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Hiệu trưởng</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Tỷ lệ tốt nghiệp THPT toàn trường</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Đạt ≥ 98.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Hàng năm</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>25 điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>DM1: Quản lý</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Hiệu trưởng</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Quyết toán ngân sách &amp; Tài chính công</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>100% đúng hạn, minh bạch</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Quý / Năm</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>20 điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>DM1: Quản lý</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Phó Hiệu trưởng</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Tiến độ chương trình &amp; Ký số học bạ</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>100% đúng tiến độ quy định</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Tháng / Kỳ</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>25 điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>DM1: Quản lý</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Tổ trưởng CM</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Sinh hoạt NCBL &amp; Đổi mới PPDH tổ</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>≥ 02 chuyên đề / học kỳ</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Hàng tháng</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>25 điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>DM1: Quản lý</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Tổ phó CM</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Nề nếp sổ sách &amp; Ký số tổ CM</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>100% thành viên đúng hạn</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Hàng tháng</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>25 điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>DM2: Chuyên môn</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên 13 môn</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Tiến độ giảng dạy &amp; Kế hoạch bài dạy</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>100% tiết dạy có giáo án chuẩn</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Hàng tuần</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>30 điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>DM2: Chuyên môn</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên 13 môn</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Chất lượng học sinh môn học phụ trách</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Học sinh đạt chuẩn ≥ 95%</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Học kỳ / Năm</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>30 điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>DM2: Chuyên môn</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên 13 môn</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Ký số học bạ &amp; Sổ điểm điện tử</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>100% đúng hạn, không sai sót</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Cuối kỳ</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>20 điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>DM2: Chuyên môn</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Giáo viên 13 môn</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Bồi dưỡng HSG cấp tỉnh / Sáng kiến</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Có giải HSG hoặc SKKN nghiệm thu</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Hàng năm</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>20 điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Năng lực chuyên môn</t>
+          <t>DM3: Hỗ trợ</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Kiểm tra đánh giá &amp; Phân tích chất lượng</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Cấp độ 4 - 5</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Cấp độ 3 - 5</t>
+          <t>Kế toán viên</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Thanh toán lương &amp; Báo cáo tài chính</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Lương trước ngày 05; 0 sai sót</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 2 - 3</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Đánh giá đúng năng lực học sinh, xây dựng ma trận đề chuẩn, phân tích dữ liệu.</t>
+          <t>Hàng tháng</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>30 điểm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Năng lực bổ trợ</t>
+          <t>DM3: Hỗ trợ</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Xử lý tình huống sư phạm &amp; Giải quyết tranh chấp</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Cấp độ 4 - 5</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Cấp độ 3 - 4</t>
+          <t>Văn thư</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Xử lý công văn đi/đến &amp; Quản lý con dấu</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>100% công văn chuyển trong ngày</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Cấp độ 2 - 3</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Điềm tĩnh, thấu tình đạt lý, giải quyết xung đột trong môi trường học đường nhân văn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16"/>
+          <t>Hàng ngày</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>30 điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>DM3: Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Thiết bị, thí nghiệm</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Chuẩn bị thiết bị thực hành &amp; An toàn PCCC</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>100% tiết thực hành sẵn sàng</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Hàng tuần</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>30 điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>DM3: Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Giáo vụ</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Sổ đăng bộ &amp; CSDL học sinh số hóa</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Chính xác 100%, đúng tiến độ</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Học kỳ / Năm</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>30 điểm</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>BỘ CHỈ SỐ KPI ĐO LƯỜNG HIỆU QUẢ ĐẦU RA CHO 35 BIÊN CHẾ</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>DM3: Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Y tế trường học</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Sơ cấp cứu, tủ thuốc &amp; Vệ sinh ATTP</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>100% an toàn học đường, 0 ngộ độc</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Thường xuyên</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>30 điểm</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>Nhóm VTVL</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>Vị trí áp dụng</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>Chỉ số KPI chính</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>Mục tiêu định lượng</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>Tần suất</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
-        <is>
-          <t>Trọng số %</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>I. Quản lý (7 người)</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Hiệu trưởng</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Tỷ lệ tốt nghiệp THPT toàn trường</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Đạt ≥ 98.5%</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Hàng năm</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>I. Quản lý (7 người)</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Phó Hiệu trưởng</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Tiến độ chương trình &amp; Ký số học bạ</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>100% đúng tiến độ &amp; ký số</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Tháng / Kỳ</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>I. Quản lý (7 người)</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Tổ trưởng CM</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Sinh hoạt NCBL &amp; Chuyên đề STEM</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>≥ 02 chuyên đề / học kỳ</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Hàng tháng</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>I. Quản lý (7 người)</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Tổ phó CM</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Lịch báo giảng &amp; Sổ sách điện tử</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>100% thành viên đúng hạn</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Hàng tuần</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>II. Chuyên môn (22 GV)</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>22 GV 13 Môn học</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Kế hoạch bài dạy &amp; Dạy 17 tiết/tuần</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>100% tiết có giáo án chuẩn</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Hàng tuần</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>II. Chuyên môn (22 GV)</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>22 GV 13 Môn học</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Chất lượng môn học phụ trách</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>Học sinh đạt chuẩn ≥ 96%</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Học kỳ / Năm</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>II. Chuyên môn (22 GV)</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>22 GV 13 Môn học</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Bồi dưỡng HSG &amp; Phụ đạo yếu kém</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>Có giải HSG cấp tỉnh</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Hàng năm</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>III. Hỗ trợ (6 người)</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Kế toán viên</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Chi trả lương &amp; Quyết toán ngân sách</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>100% đúng hạn, kiểm toán tốt</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Hàng tháng</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>III. Hỗ trợ (6 người)</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Văn thư</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Xử lý công văn đi đến trên iOffice</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>100% xử lý trong ngày</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>DM3: Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Thủ quỹ</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Quản lý quỹ tiền mặt &amp; Khớp sổ quỹ</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Khớp 100% số dư với kế toán</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Hàng ngày</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>III. Hỗ trợ (6 người)</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Thiết bị, TN</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Chuẩn bị thiết bị cho tiết thực hành</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>100% tiết thực hành đủ đồ dùng</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Hàng tuần</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>III. Hỗ trợ (6 người)</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Giáo vụ</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Sổ đăng bộ, Tuyển sinh 10 &amp; Thi TN</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>100% hồ sơ chính xác, đúng hạn</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Hàng kỳ</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>III. Hỗ trợ (6 người)</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Y tế học đường</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Chăm sóc sức khỏe &amp; Phòng chống dịch</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>100% HS theo dõi sức khỏe</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Hàng kỳ</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>III. Hỗ trợ (6 người)</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Thủ quỹ</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Quản lý két tiền mặt &amp; Khớp số dư</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>Khớp số dư 100%, an toàn</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Hàng ngày</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>35%</t>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>30 điểm</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:G2"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Bang-mo-ta-De-an-VTVL-THPT-Phuc-Hoa-ND232-2026.xlsx
+++ b/Bang-mo-ta-De-an-VTVL-THPT-Phuc-Hoa-ND232-2026.xlsx
@@ -1955,15 +1955,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="68" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="49" customWidth="1" min="6" max="6"/>
+    <col width="61" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2007,28 +2007,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A4" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Hiệu trưởng
 (HT-THPT-01)
-Phụ cấp: 0.70 | 01 người
-Định mức: 02 tiết/tuần</t>
+Bậc 3 đến Bậc 5 | 01 người
+Phụ cấp: 0.70 | Định mức: 02 tiết/tuần</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>1. Chiến lược &amp; Kế hoạch phát triển</t>
+          <t>1. Chiến lược &amp; Kế hoạch phát triển trường</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>- Xây dựng Chiến lược 5 năm, Kế hoạch năm học trình cấp có thẩm quyền phê duyệt.
-- Ban hành Quy chế dân chủ, Quy chế chi tiêu nội bộ, Quy chế làm việc của trường.</t>
+          <t>- Xây dựng Chiến lược phát triển trường 5 năm, Kế hoạch GD nhà trường theo CT GDPT 2018.
+- Ban hành Bộ Quy chế quản trị nội bộ trước ngày 05/9 hàng năm.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -2038,32 +2036,29 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>- Chiến lược phát triển trường 5 năm.
+          <t>- Chiến lược phát triển trường 2026-2030.
 - Kế hoạch năm học &amp; Quy chế làm việc.
 - Báo cáo định kỳ Sở GD&amp;ĐT.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Hiệu trưởng
-(HT-THPT-01)</t>
+      <c r="A5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Hiệu trưởng (tiếp)</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>2. Quản lý nhân sự &amp; Đánh giá thi đua</t>
+          <t>2. Quản lý nhân sự &amp; Đánh giá viên chức</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>- Phân công nhiệm vụ, bổ nhiệm tổ trưởng, tổ phó; đánh giá xếp loại VC hàng năm theo NĐ 232/2026/NĐ-CP.
+          <t>- Phân công nhiệm vụ, bổ nhiệm TTCM/TPCM; đánh giá xếp loại viên chức theo NĐ 232/2026/NĐ-CP.
 - Thực hiện công tác quy hoạch, đào tạo, bồi dưỡng và thi đua khen thưởng.</t>
         </is>
       </c>
@@ -2075,32 +2070,29 @@
       <c r="F5" s="8" t="inlineStr">
         <is>
           <t>- QĐ phân công nhiệm vụ cán bộ giáo viên.
-- QĐ xếp loại thi đua, khen thưởng viên chức.
-- Hồ sơ quy hoạch cán bộ quản lý.</t>
+- QĐ bổ nhiệm TTCM/TPCM.
+- Hồ sơ xếp loại thi đua, khen thưởng viên chức.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Hiệu trưởng
-(HT-THPT-01)</t>
+      <c r="A6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Hiệu trưởng (tiếp)</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>3. Quản lý tài chính &amp; Cơ sở vật chất</t>
+          <t>3. Quản lý tài chính &amp; Tài sản công</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>- Chủ tài khoản, duyệt thu - chi ngân sách, kiểm tra công tác kế toán, quản lý tài sản công đúng luật.
-- Chỉ đạo sửa chữa, nâng cấp CSVC trường học bảo đảm dạy và học an toàn.</t>
+          <t>- Chủ tài khoản, duyệt thu - chi ngân sách theo Luật Ngân sách và Luật Kế toán; quản lý tài sản công đúng luật.
+- Chỉ đạo sửa chữa CSVC, mua sắm TBDH; bảo đảm môi trường sư phạm an toàn.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -2110,33 +2102,30 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>- Dự toán &amp; Báo cáo quyết toán ngân sách.
+          <t>- Dự toán &amp; Báo cáo quyết toán năm.
 - Quy chế chi tiêu nội bộ chuẩn hóa.
 - Báo cáo kiểm kê tài sản hàng năm.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Hiệu trưởng
-(HT-THPT-01)</t>
+      <c r="A7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Hiệu trưởng (tiếp)</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>4. Chỉ đạo chuyên môn &amp; Giảng dạy</t>
+          <t>4. Chỉ đạo chuyên môn, kỳ thi &amp; KĐCLGD</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>- Chỉ đạo kỳ thi tốt nghiệp THPT, kỳ thi chọn HSG; trực tiếp giảng dạy 02 tiết/tuần theo quy định.
-- Thanh tra nội bộ, dự giờ thăm lớp, đổi mới PPDH và ứng dụng AI toàn trường.</t>
+          <t>- Chỉ đạo kỳ thi tốt nghiệp THPT (mục tiêu đỗ ≥ 98.5%), thi tuyển sinh 10, thi chọn HSG tỉnh.
+- Chỉ đạo công tác kiểm định chất lượng giáo dục, duy trì trường đạt chuẩn quốc gia.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -2147,158 +2136,541 @@
       <c r="F7" s="8" t="inlineStr">
         <is>
           <t>- Báo cáo kết quả kỳ thi tốt nghiệp THPT.
-- Sổ giáo án cá nhân giảng dạy 02 tiết/tuần.
-- Biên bản kiểm tra chuyên môn nội bộ.</t>
+- Báo cáo kết quả thi HSG cấp tỉnh.
+- Hồ sơ tự đánh giá KĐCLGD.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="A8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Hiệu trưởng (tiếp)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>5. Chuyển đổi số, an toàn trường học &amp; Giảng dạy</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>- Chỉ đạo 100% học bạ số ký đúng hạn, ứng dụng AI toàn trường; xây dựng trường học an toàn, hạnh phúc.
+- Trực tiếp giảng dạy đúng định mức 02 tiết/tuần theo quy định.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>- 100% học bạ số được phê duyệt đúng hạn.
+- Kế hoạch CĐS và ứng dụng AI.
+- Sổ giáo án cá nhân giảng dạy 02 tiết/tuần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Phó Hiệu trưởng
 (PHT-THPT-01)
-Phụ cấp: 0.50 | 02 người
-Định mức: 04 tiết/tuần</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>1. Chỉ đạo &amp; điều hành chuyên môn</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>- Thẩm định và duyệt Kế hoạch giáo dục nhà trường, kế hoạch các tổ CM theo CT GDPT 2018.
-- Chỉ đạo đổi mới phương pháp dạy học, giáo dục STEM/STEAM, chuyển đổi số dạy học.</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
+Bậc 3 đến Bậc 5 | 02 người
+Phụ cấp: 0.50 | Định mức: 04 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>1. Chỉ đạo &amp; điều hành chuyên môn dạy học</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>- Thẩm định và duyệt Kế hoạch dạy học của các tổ; chỉ đạo xếp thời khóa biểu khoa học.
+- Theo dõi lịch báo giảng, kế hoạch dạy bù/thay; bảo đảm tiến độ chương trình 100%.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>- Kế hoạch chuyên môn năm học được phê duyệt.
-- Lịch thi, thời khóa biểu toàn trường.
+- Thời khóa biểu toàn trường.
 - Báo cáo sơ kết, tổng kết chuyên môn.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Phó Hiệu trưởng
-(PHT-THPT-01)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>2. Khảo thí, ôn thi TN &amp; Ký số học bạ</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>- Xây dựng ma trận đặc tả, ngân hàng đề kiểm tra định kỳ; quản lý ôn thi TN THPT khối 12.
-- Kiểm tra, ký duyệt học bạ điện tử, kiểm tra hồ sơ giáo án giáo viên; dạy 04 tiết/tuần.</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Phó Hiệu trưởng (tiếp)</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>2. Chỉ đạo khảo thí, ôn thi TN &amp; thi HSG</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>- Xây dựng ma trận đặc tả, ngân hàng đề kiểm tra định kỳ; tổ chức ôn thi TN THPT khối 12.
+- Phân tích phổ điểm thi thử; chỉ đạo bồi dưỡng HSG các môn thi cấp tỉnh.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>- Ngân hàng đề kiểm tra định kỳ chuẩn quy chế.
-- Kế hoạch ôn thi TN THPT chi tiết theo môn.
-- 100% học bạ số được duyệt đúng hạn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Tổ trưởng CM
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>- Ngân hàng đề kiểm tra định kỳ.
+- Kế hoạch và lịch ôn thi TN THPT chi tiết.
+- Danh sách học sinh đạt giải HSG tỉnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Phó Hiệu trưởng (tiếp)</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>3. Kiểm tra chuyên môn nội bộ &amp; Dự giờ</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>- Kiểm tra nội bộ 100% giáo viên theo kế hoạch; trực tiếp dự giờ 1-2 tiết/tuần.
+- Tổ chức Hội thi GVDG cấp trường; bồi dưỡng giáo viên tham dự thi cấp tỉnh.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch và biên bản kiểm tra nội bộ.
+- Phiếu dự giờ giáo viên.
+- Hồ sơ Hội thi GVDG cấp trường.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Phó Hiệu trưởng (tiếp)</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>4. Phụ trách CSVC, thiết bị dạy học &amp; Hoạt động GD</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>- Quản lý khai thác phòng bộ môn, phòng máy vi tính, thiết bị dạy học.
+- Chỉ đạo hoạt động trải nghiệm, hướng nghiệp; thay mặt HT khi được ủy quyền.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch sử dụng CSVC và thiết bị dạy học.
+- Báo cáo kiểm kê thiết bị định kỳ.
+- Biên bản xử lý công việc khi được ủy quyền.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Phó Hiệu trưởng (tiếp)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>5. Chuyển đổi số, ký số học bạ &amp; Giảng dạy</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>- Đôn đốc ký số học bạ đúng hạn 100%; kiểm tra việc vào điểm số điện tử.
+- Trực tiếp giảng dạy 04 tiết/tuần theo phân công chuyên môn.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>- 100% học bạ số được ký duyệt đúng hạn.
+- Sổ theo dõi tiến độ điểm số.
+- Sổ giáo án cá nhân giảng dạy 04 tiết/tuần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Tổ trưởng chuyên môn
 (TTCM-THPT-01)
-Phụ cấp: 0.25 | 02 người
-Định mức: 14 tiết/tuần</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>1. Quản lý toàn diện chuyên môn tổ</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>- Xây dựng kế hoạch dạy học môn học (PL1, PL2, PL3) theo CT GDPT 2018; phân công GV dạy đúng chuyên ngành.
-- Tổ chức sinh hoạt chuyên môn theo NCBL (≥ 2 lần/tháng); kiểm tra giáo án, dự giờ GV.</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>- Kế hoạch giáo dục tổ chuyên môn.
-- Biên bản họp sinh hoạt chuyên môn theo NCBL.
-- Phiếu đánh giá giáo viên trong tổ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Tổ phó CM
+Bậc 3 đến Bậc 4 | 02 người
+Phụ cấp: 0.25 | Định mức: 14 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>1. Quản lý toàn diện chuyên môn tổ &amp; Kế hoạch dạy học</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>- Xây dựng và thực hiện kế hoạch dạy học môn học (PL1, PL2, PL3) theo CT GDPT 2018.
+- Phân công giáo viên giảng dạy đúng chuyên môn và năng lực.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch giáo dục tổ chuyên môn (PL1, PL2, PL3).
+- Bảng phân công nhiệm vụ giáo viên trong tổ.
+- Lịch sinh hoạt tổ chuyên môn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Tổ trưởng chuyên môn (tiếp)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>2. Sinh hoạt chuyên môn theo NCBL &amp; Đổi mới PPDH</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>- Tổ chức sinh hoạt chuyên môn theo NCBL (≥ 2 lần/tháng); đổi mới PPDH tích cực, STEM.
+- Ứng dụng AI hỗ trợ soạn giảng, tạo đề kiểm tra đánh giá năng lực.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>- Biên bản họp sinh hoạt tổ theo NCBL.
+- Chuyên đề đổi mới PPDH hoặc bài học STEM.
+- Kho học liệu số của tổ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Tổ trưởng chuyên môn (tiếp)</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>3. Kiểm tra hồ sơ giáo án, dự giờ &amp; Đánh giá tổ viên</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>- Kiểm tra giáo án, hồ sơ chuyên môn của tổ viên hàng tháng; dự giờ 2-3 tiết/kỳ/GV.
+- Đánh giá chuẩn nghề nghiệp giáo viên cuối năm học.</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>- Sổ kiểm tra hồ sơ chuyên môn tổ.
+- Phiếu đánh giá dự giờ giáo viên.
+- Hồ sơ đánh giá chuẩn nghề nghiệp tổ viên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Tổ trưởng chuyên môn (tiếp)</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>4. Bồi dưỡng học sinh giỏi &amp; Phụ đạo học sinh yếu</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>- Xây dựng kế hoạch bồi dưỡng đội tuyển HSG môn học tham dự thi cấp tỉnh.
+- Theo dõi và phân công phụ đạo học sinh có nguy cơ chưa đạt chuẩn.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>- Kế hoạch bồi dưỡng HSG và phụ đạo của tổ.
+- Danh sách học sinh đội tuyển.
+- Kết quả học sinh đạt giải HSG cấp tỉnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Tổ trưởng chuyên môn (tiếp)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>5. Giảng dạy 14 tiết/tuần &amp; Làm gương chuyên môn</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy đủ 14 tiết/tuần (được giảm 3 tiết); đi đầu trong đổi mới phương pháp.
+- Hoàn thành nhận xét, ký số học bạ đúng thời hạn quy định.</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>- 100% tiết dạy có giáo án chuẩn bị chu đáo.
+- Học bạ số ký duyệt đúng hạn.
+- Học sinh lớp phụ trách đạt kết quả cao.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Tổ phó chuyên môn
 (TPCM-THPT-01)
-Phụ cấp: 0.15 | 02 người
-Định mức: 16 tiết/tuần</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>1. Quản lý nề nếp, sổ sách &amp; tiến độ</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>- Theo dõi tiến độ chương trình hàng tuần, lịch báo giảng điện tử, kế hoạch dạy thay/bù của tổ viên.
-- Kiểm tra nề nếp hồ sơ sổ sách, đôn đốc ký số học bạ; giảng dạy 16 tiết/tuần.</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+Bậc 3 đến Bậc 4 | 02 người
+Phụ cấp: 0.15 | Định mức: 16 tiết/tuần</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>1. Theo dõi tiến độ chương trình &amp; Kế hoạch dạy bù/thay</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>- Giúp Tổ trưởng theo dõi sát tiến độ chương trình hàng tuần của các thành viên trong tổ.
+- Lập kế hoạch dạy bù, dạy thay kịp thời, bảo đảm tiến độ.</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>- Sổ theo dõi tiến độ chương trình hàng tuần.
+- Bảng tổng hợp lịch dạy bù, dạy thay.
+- Báo cáo tiến độ chương trình định kỳ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Tổ phó chuyên môn (tiếp)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>2. Đôn đốc lập lịch báo giảng &amp; Kiểm tra hồ sơ</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>- Đôn đốc các thành viên cập nhật lịch báo giảng điện tử đúng hạn đầu tuần.
+- Hỗ trợ Tổ trưởng kiểm tra nề nếp hồ sơ sổ sách chuyên môn.</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>- Lịch báo giảng điện tử của tổ đúng hạn 100%.
 - Biên bản kiểm tra nề nếp hồ sơ chuyên môn.
-- Báo cáo tổng hợp nề nếp tổ viên.</t>
+- Sổ tích lũy chuyên môn cá nhân.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Tổ phó chuyên môn (tiếp)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>3. Kiểm tra thiết bị dạy học &amp; Sử dụng phòng bộ môn</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>- Theo dõi, đôn đốc việc mượn và sử dụng thiết bị dạy học, hóa chất, phòng thực hành bộ môn của tổ viên.</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>- Sổ theo dõi mượn thiết bị và phòng bộ môn.
+- Phiếu đề xuất sửa chữa, bổ sung thiết bị dạy học của tổ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Tổ phó chuyên môn (tiếp)</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>4. Đôn đốc cập nhật điểm số &amp; Ký số học bạ</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>- Theo dõi tiến độ kiểm tra đánh giá, vào điểm số điện tử và ký số học bạ của các giáo viên trong tổ; bảo đảm không trễ hạn.</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>- Báo cáo tiến độ điểm số của tổ.
+- 100% thành viên ký số học bạ đúng hạn.
+- Không có vi phạm quy chế chuyên môn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Tổ phó chuyên môn (tiếp)</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>5. Giảng dạy 16 tiết/tuần &amp; Điều hành khi ủy quyền</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>- Giảng dạy đủ 16 tiết/tuần (được giảm 1 tiết); thay mặt Tổ trưởng điều hành tổ khi được ủy quyền.</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>- Giáo án cá nhân giảng dạy 16 tiết/tuần.
+- Biên bản điều hành họp tổ khi Tổ trưởng vắng mặt.
+- Lớp phụ trách đạt chỉ tiêu giao.</t>
         </is>
       </c>
     </row>
@@ -4678,7 +5050,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Giáo viên trung học phổ thông (Giáo viên 13 môn học trong Phụ lục I) / Viên chức Hỗ trợ</t>
+          <t>Giáo viên trung học phổ thông (Giáo viên 13 môn học trong Phụ lục I) / Viên chức Hỗ trợ / Viên chức Quản lý</t>
         </is>
       </c>
       <c r="D7" s="8" t="n"/>
@@ -4697,7 +5069,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>GV-THPT-01 (Chuyên môn) | KT, VT, TBTN, GVU, YT, TQ (Hỗ trợ)</t>
+          <t>HT, PHT, TTCM, TPCM (Quản lý) | GV-THPT-01 (13 Môn) | KT, VT, TBTN, GVU, YT, TQ (Hỗ trợ)</t>
         </is>
       </c>
       <c r="D8" s="8" t="n"/>
@@ -4716,7 +5088,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Chuyên môn: Bậc 3 đến Bậc 4 | Hỗ trợ: Bậc 1 đến Bậc 4</t>
+          <t>Quản lý &amp; Chuyên môn: Bậc 3 đến Bậc 5 | Hỗ trợ: Bậc 1 đến Bậc 4</t>
         </is>
       </c>
       <c r="D9" s="8" t="n"/>
@@ -4773,7 +5145,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Giáo viên: 17 tiết/tuần | Viên chức hỗ trợ: 40 giờ/tuần</t>
+          <t>Hiệu trưởng: 2t/t | Phó HT: 4t/t | TTCM: 14t/t | TPCM: 16t/t | Giáo viên 13 môn: 17 tiết/tuần | Viên chức hỗ trợ: 40 giờ/tuần</t>
         </is>
       </c>
       <c r="D12" s="8" t="n"/>
@@ -4793,7 +5165,7 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Đảm nhận nhiệm vụ giảng dạy và giáo dục học sinh theo Chương trình GDPT 2018 (đối với GV 13 môn học) và bảo đảm các điều kiện về tài chính, văn thư, thiết bị thí nghiệm, giáo vụ, y tế học đường, ngân quỹ phục vụ vận hành thông suốt của nhà trường (đối với 06 viên chức hỗ trợ).</t>
+          <t>Lãnh đạo, quản lý và điều hành đơn vị sự nghiệp công lập (đối với Ban Giám hiệu, TTCM, TPCM); đảm nhận nhiệm vụ giảng dạy và giáo dục học sinh theo Chương trình GDPT 2018 (đối với GV 13 môn học); và bảo đảm các điều kiện về tài chính, văn thư, thiết bị thí nghiệm, giáo vụ, y tế học đường, quỹ tiền mặt phục vụ vận hành thông suốt của nhà trường (đối với 06 viên chức hỗ trợ).</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
@@ -4815,7 +5187,7 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Chi tiết cụ thể theo từng môn học và từng vị trí hỗ trợ được quy định tại Sheet 3 (Quản lý), Sheet 4 (13 Môn học Chuyên môn) và Sheet 5 (06 Vị trí Hỗ trợ).</t>
+          <t>Chi tiết cụ thể theo từng chức danh quản lý, từng môn học và từng vị trí hỗ trợ được quy định tại Sheet 3 (Quản lý 7 BC), Sheet 4 (13 Môn học Chuyên môn 22 BC) và Sheet 5 (06 Vị trí Hỗ trợ 6 BC).</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
@@ -4841,8 +5213,11 @@
  - Đạo đức nghề nghiệp, liêm chính sư phạm, phục vụ nhân dân (Cấp độ 4 - 5)
  - Kỷ luật, trách nhiệm và tinh thần hợp tác đồng nghiệp (Cấp độ 4 - 5)
  - Đổi mới sáng tạo, chuyển đổi số và ứng dụng AI (Cấp độ 3 - 4)
-2. Năng lực chuyên môn nghiệp vụ:
- - Nắm vững kiến thức bộ môn theo CT GDPT 2018 (Cấp độ 4 - 5)
+2. Năng lực quản lý (dành cho Ban Giám hiệu, TTCM, TPCM):
+ - Tư duy chiến lược, lập kế hoạch và tổ chức điều hành (Cấp độ 4 - 5)
+ - Quản trị nhân lực, kiểm tra giám sát và đánh giá viên chức (Cấp độ 4 - 5)
+3. Năng lực chuyên môn nghiệp vụ:
+ - Nắm vững kiến thức 13 bộ môn theo CT GDPT 2018 (Cấp độ 4 - 5)
  - Kỹ năng sư phạm, tổ chức hoạt động học tập, dạy học STEM (Cấp độ 4 - 5)
  - Đánh giá năng lực học sinh theo thông tư Bộ GD&amp;ĐT (Cấp độ 4)</t>
         </is>
@@ -4913,7 +5288,7 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>- Về trình độ đào tạo: Bằng Cử nhân (Đại học) sư phạm trở lên đúng chuyên ngành đối với Giáo viên; Bằng Đại học/Cao đẳng/Trung cấp chuyên ngành phù hợp đối với Viên chức hỗ trợ (Kế toán, Văn thư, Thiết bị, Y tế...).
+          <t>- Về trình độ đào tạo: Bằng Cử nhân (Đại học) sư phạm trở lên đúng chuyên ngành đối với Giáo viên và Cán bộ quản lý; Bằng Đại học/Cao đẳng/Trung cấp chuyên ngành phù hợp đối với Viên chức hỗ trợ (Kế toán, Văn thư, Thiết bị, Y tế, Thủ quỹ...).
 - Về chứng chỉ: Có chứng chỉ bồi dưỡng tiêu chuẩn chức danh nghề nghiệp viên chức theo quy định.
 - Về kỹ năng số: Sử dụng thành thạo máy vi tính, phần mềm quản lý giáo dục điện tử, ký số học bạ, khai thác công cụ AI hỗ trợ công việc.
 - Phẩm chất đạo đức: Mẫu mực, tâm huyết với sự nghiệp giáo dục vùng cao Phục Hòa.</t>
